--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -1959,7 +1959,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充 · 02-技能请向右滚动至 I 列</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充 · 02-技能请向右滚动至 I 列</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>常见问题 · 2026-07-06-v2</t>
+          <t>常见问题 · 2026-07-06-v3</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>版本 2026-07-06-v2 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充 · 汇总页；各表右侧绿底列为可编辑 FAQ</t>
+          <t>版本 2026-07-06-v3 · 各表表格最右列为【常见问题】（浅绿底），可直接编辑补充 · 汇总页；各表右侧绿底列为可编辑 FAQ</t>
         </is>
       </c>
     </row>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -1393,7 +1393,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6477000" cy="3895725"/>
+    <ext cx="6019800" cy="4476750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1415,7 +1415,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1907,14 +1907,14 @@
     <row r="5" outlineLevel="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>参考数据：Runes of Aldur · Lv.98 Oracle（poe.ninja 面板快照）</t>
+          <t>参考数据：Runes of Aldur · Lv.99 Oracle（poe.ninja 面板快照）</t>
         </is>
       </c>
     </row>
     <row r="6" outlineLevel="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>数据更新：2026-07-07 · PoE2 0.5.4</t>
+          <t>数据更新：2026-07-12 · PoE2 0.5.4</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>68（I组面板）</t>
+          <t>63（I组面板）</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>6,767</t>
+          <t>6,713</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Str 仅 68+6，只能选低需求盾底</t>
+          <t>Str 仅 63+6，只能选低需求盾底</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4852,7 +4852,7 @@
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>图例：蓝 = 升华轮盘 · 浅蓝 = 未见之道 · 红 = 基石 · 黄 = notable · 灰 = 普通小点
-已点节点数：112（来源 poe.ninja passiveSelection）</t>
+已点节点数：114（来源 poe.ninja passiveSelection）</t>
         </is>
       </c>
     </row>
@@ -4885,178 +4885,94 @@
     <row r="32" outlineLevel="1"/>
     <row r="33" outlineLevel="1"/>
     <row r="34" outlineLevel="1"/>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>▸ 职业与升华</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>基础职业</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>德鲁伊（Druid）</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>角色底层职业</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>使用升华</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>天启先知（Oracle）</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>升华试炼选择</t>
-        </is>
-      </c>
-    </row>
+    <row r="35" outlineLevel="1"/>
+    <row r="36" outlineLevel="1"/>
+    <row r="37" outlineLevel="1"/>
+    <row r="38" outlineLevel="1"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>▸ 基石与核心天赋</t>
+          <t>▸ 职业与升华</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>作用</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>基石</t>
+          <t>基础职业</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Pain Attunement</t>
+          <t>德鲁伊（Druid）</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>已点</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>角色底层职业</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>基石</t>
+          <t>使用升华</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Ancestral Bond</t>
+          <t>天启先知（Oracle）</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>已点</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>基石</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Mind Over Matter</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>已点</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>升华试炼选择</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>▸ 基石与核心天赋</t>
         </is>
       </c>
     </row>
     <row r="44" outlineLevel="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>基石</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Scarred Faith</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>已点</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -5068,7 +4984,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Elemental Equilibrium</t>
+          <t>Pain Attunement</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -5090,7 +5006,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Wildsurge Incantation</t>
+          <t>Ancestral Bond</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -5107,230 +5023,210 @@
     <row r="47" outlineLevel="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>涂油</t>
+          <t>基石</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>Mind Over Matter</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>每诅咒 +30% 伤害，-30% 诅咒效果</t>
+          <t>已点</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>核心</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48" outlineLevel="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>武器组 I</t>
+          <t>基石</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>24 点</t>
+          <t>Scarred Faith</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>冰霜/法术/暴击/图腾伤害</t>
+          <t>已点</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>输出专精</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>武器组 II</t>
+          <t>基石</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>24 点</t>
+          <t>Elemental Equilibrium</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>护甲/抗性/法力/格挡</t>
+          <t>已点</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>生存专精</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>▸ 升华试炼天赋（8 点 · 天启先知轮盘）</t>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>基石</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Wildsurge Incantation</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>已点</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51" outlineLevel="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>天赋</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>校验</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>涂油</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Warding Fetish</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>每诅咒 +30% 伤害，-30% 诅咒效果</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>核心</t>
         </is>
       </c>
     </row>
     <row r="52" outlineLevel="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>武器组 I</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>虛實交織</t>
+          <t>24 点</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>已配置基石中型范围内未连接的非基石天赋仍可配置</t>
+          <t>冰霜/法术/暴击/图腾伤害</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>升华核心</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
+          <t>输出专精</t>
         </is>
       </c>
     </row>
     <row r="53" outlineLevel="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>武器组 II</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>未見之道</t>
+          <t>24 点</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>踏上未履之道；解锁先知专属天赋树分支</t>
+          <t>护甲/抗性/法力/格挡</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>升华核心</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" outlineLevel="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>無名心木</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>+1 召唤图腾上限；图腾生命归零后 6 秒死亡</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>升华核心</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
+          <t>生存专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>▸ 升华试炼天赋（8 点 · 天启先知轮盘）</t>
         </is>
       </c>
     </row>
     <row r="55" outlineLevel="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>微小損害</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>敌人对你暴击率不幸；敌人击中你伤害不幸</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>升华核心</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>天赋</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>校验</t>
         </is>
       </c>
     </row>
     <row r="56" outlineLevel="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>天赋点</t>
+          <t>虛實交織</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点天赋点</t>
+          <t>已配置基石中型范围内未连接的非基石天赋仍可配置</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>升华小点</t>
+          <t>升华核心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -5342,22 +5238,22 @@
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>天赋点</t>
+          <t>未見之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>获得 1 点天赋点</t>
+          <t>踏上未履之道；解锁先知专属天赋树分支</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>升华小点</t>
+          <t>升华核心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -5369,22 +5265,22 @@
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>對你的暴擊傷害加成</t>
+          <t>無名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>击中你的伤害减少 12% 暴击伤害加成</t>
+          <t>+1 召唤图腾上限；图腾生命归零后 6 秒死亡</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>升华小点</t>
+          <t>升华核心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -5396,83 +5292,103 @@
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>圖騰攻擊及施放速度</t>
+          <t>微小損害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>图腾法术施放速度 +5%；图腾攻击速度 +5%</t>
+          <t>敌人对你暴击率不幸；敌人击中你伤害不幸</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
+          <t>升华核心</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>天赋点</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>获得 1 点天赋点</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>✓poe2db</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>▸ 未见之道天赋（8 点 · 需先点「未见之道」）</t>
-        </is>
-      </c>
-    </row>
     <row r="61" outlineLevel="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>天赋</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>校验</t>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>天赋点</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>获得 1 点天赋点</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>升华小点</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
         </is>
       </c>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>精算獵者</t>
+          <t>對你的暴擊傷害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>减少 5% 技能速度；提高 50% 暴击率</t>
+          <t>击中你的伤害减少 12% 暴击伤害加成</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>升华核心</t>
+          <t>升华小点</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5484,22 +5400,22 @@
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>同袍情誼</t>
+          <t>圖騰攻擊及施放速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>提高 30% 伤害；召唤物造成 30% 更多伤害</t>
+          <t>图腾法术施放速度 +5%；图腾攻击速度 +5%</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>升华核心</t>
+          <t>升华小点</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -5508,79 +5424,59 @@
         </is>
       </c>
     </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>暴擊傷害</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>提高 20% 暴击伤害加成</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>升华小点</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>▸ 未见之道天赋（8 点 · 需先点「未见之道」）</t>
         </is>
       </c>
     </row>
     <row r="65" outlineLevel="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>暴擊傷害</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>提高 20% 暴击伤害加成</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>升华小点</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>天赋</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>校验</t>
         </is>
       </c>
     </row>
     <row r="66" outlineLevel="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>精算獵者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>提高 20% 暴击伤害加成</t>
+          <t>减少 5% 技能速度；提高 50% 暴击率</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>升华小点</t>
+          <t>升华核心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5592,22 +5488,22 @@
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>同袍情誼</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>提高 15% 伤害；召唤物造成 15% 更多伤害</t>
+          <t>提高 30% 伤害；召唤物造成 30% 更多伤害</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>升华小点</t>
+          <t>升华核心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -5619,17 +5515,17 @@
     <row r="68" outlineLevel="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>提高 15% 伤害；召唤物造成 15% 更多伤害</t>
+          <t>提高 20% 暴击伤害加成</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -5646,585 +5542,693 @@
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
+          <t>暴擊傷害</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>提高 20% 暴击伤害加成</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>升华小点</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>暴擊傷害</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>提高 20% 暴击伤害加成</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>升华小点</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
           <t>傷害和召喚物傷害</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>提高 15% 伤害；召唤物造成 15% 更多伤害</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>✓poe2db</t>
         </is>
       </c>
     </row>
-    <row r="70" outlineLevel="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>▸ 武器组 I 天赋要点（24 点 · 伤害）</t>
-        </is>
-      </c>
-    </row>
     <row r="72" outlineLevel="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>优先词缀类</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>傷害和召喚物傷害</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>提高 15% 伤害；召唤物造成 15% 更多伤害</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>升华小点</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
         </is>
       </c>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>傷害和召喚物傷害</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>提高 15% 伤害；召唤物造成 15% 更多伤害</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>升华小点</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>▸ 武器组 I 天赋要点（24 点 · 伤害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>优先词缀类</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>冰霜 / 法术 / 暴击 / 图腾伤害</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Grim Pillars 主输出</t>
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>图腾</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>图腾数量、施放速度、生命</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>配合 Ancestral Bond + Heartwood</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" outlineLevel="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>诅咒</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>诅咒效果、额外诅咒槽</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Blasphemy 链路</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" outlineLevel="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>法力</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>最大法力、回复、Archmage 协同</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>MoM + EB 第二血条</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>▸ 武器组 II 天赋要点（24 点 · 防御）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>优先词缀类</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>护甲</t>
+          <t>诅咒</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>护甲%、元素承伤转护甲</t>
+          <t>诅咒效果、额外诅咒槽</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>物承伤尖刺时切换</t>
+          <t>Blasphemy 链路</t>
         </is>
       </c>
     </row>
     <row r="80" outlineLevel="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
+          <t>法力</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>最大法力、回复、Archmage 协同</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>MoM + EB 第二血条</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>▸ 武器组 II 天赋要点（24 点 · 防御）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>优先词缀类</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>护甲</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>护甲%、元素承伤转护甲</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>物承伤尖刺时切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
           <t>抗性</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>全抗 / 闪电抗补满</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>配合 Eternal Spark +30%</t>
         </is>
       </c>
     </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="85" outlineLevel="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>格挡</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>格挡率与格挡效果</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>当前 0%，可选投资</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>法力</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>保留与 Spirit 相关</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>双勾技能不灰</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>▸ 加点顺序（待补充 · 占位模板）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" outlineLevel="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>后续可按 PoB 导出或开荒录像填写具体节点名称与顺序。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" outlineLevel="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>阶段</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>天赋/节点</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="86" outlineLevel="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>法力</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>开荒</t>
+          <t>保留与 Spirit 相关</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>（待填）图腾 / 法术基础小点</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Act 1–2 清图与 Boss</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" outlineLevel="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>中期</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>（待填）Spell Totem + 诅咒链路</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Bone Cage → Grim Pillars 转折</t>
+          <t>双勾技能不灰</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>▸ 加点顺序（待补充 · 占位模板）</t>
         </is>
       </c>
     </row>
     <row r="88" outlineLevel="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>成型</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>（待填）MoM / EB / Archmage 路径</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>法力池与低血 PA</t>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>后续可按 PoB 导出或开荒录像填写具体节点名称与顺序。</t>
         </is>
       </c>
     </row>
     <row r="89" outlineLevel="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>升华</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>（待填）轮盘 8 点顺序</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Entwined → Unseen Path → Heartwood…</t>
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>天赋/节点</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="90" outlineLevel="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>毕业</t>
+          <t>开荒</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>（待填）未见之道 8 点</t>
+          <t>（待填）图腾 / 法术基础小点</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>暴击 / 伤害小点收尾</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>▸ 过渡计划（待补充 · 占位模板）</t>
+          <t>Act 1–2 清图与 Boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" outlineLevel="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>（待填）Spell Totem + 诅咒链路</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Bone Cage → Grim Pillars 转折</t>
         </is>
       </c>
     </row>
     <row r="92" outlineLevel="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>记录等级里程碑、天赋重洗与装备更换节点，便于复刻开荒路线。</t>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>成型</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>（待填）MoM / EB / Archmage 路径</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>法力池与低血 PA</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>天赋变化</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>装备变化</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>升华</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>（待填）轮盘 8 点顺序</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Entwined → Unseen Path → Heartwood…</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Lv.28 前</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>毕业</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>（待填）</t>
+          <t>（待填）未见之道 8 点</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>基础图腾开荒</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" outlineLevel="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Lv.45</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>诅咒 + 低血过渡</t>
+          <t>暴击 / 伤害小点收尾</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>▸ 过渡计划（待补充 · 占位模板）</t>
         </is>
       </c>
     </row>
     <row r="96" outlineLevel="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Lv.65</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Soul Mantle 入手</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>自诅咒伤害链启动</t>
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>记录等级里程碑、天赋重洗与装备更换节点，便于复刻开荒路线。</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Lv.80+</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>II 组装备就位</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>洗 24 点防御专精</t>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>天赋变化</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>装备变化</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="98" outlineLevel="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
+          <t>Lv.28 前</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>基础图腾开荒</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" outlineLevel="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Lv.45</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>诅咒 + 低血过渡</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Lv.65</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Soul Mantle 入手</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>自诅咒伤害链启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" outlineLevel="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Lv.80+</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>II 组装备就位</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>洗 24 点防御专精</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
           <t>毕业</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>（待填）</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>全暗金 + 涂油</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>对照 ninja 快照微调</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>▸ Warding Fetish 涂油（贴图）</t>
         </is>
       </c>
     </row>
-    <row r="100" outlineLevel="1">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="104" outlineLevel="1">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>部位</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>贴图</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>装备词条</t>
         </is>
       </c>
     </row>
-    <row r="101" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
+    <row r="105" outlineLevel="1" ht="28" customHeight="1">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>涂油</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>守護神器
 (Warding Fetish)</t>
         </is>
       </c>
-      <c r="C101" s="15" t="n"/>
-    </row>
-    <row r="102" outlineLevel="1" ht="132" customHeight="1">
-      <c r="A102" s="12" t="n"/>
-      <c r="B102" s="13" t="inlineStr"/>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C105" s="15" t="n"/>
+    </row>
+    <row r="106" outlineLevel="1" ht="132" customHeight="1">
+      <c r="A106" s="12" t="n"/>
+      <c r="B106" s="13" t="inlineStr"/>
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>守護神器 (Warding Fetish)
 ■ 你身上每有一個詛咒，增加30%傷害
@@ -6236,27 +6240,27 @@
         </is>
       </c>
     </row>
-    <row r="103" outlineLevel="1"/>
+    <row r="107" outlineLevel="1"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="B105:C105"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A105:A106"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A96:F96"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6317,7 +6321,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Grim Pillars 414,709</t>
+          <t>Grim Pillars 436,868</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -608,7 +608,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>26</row>
       <rowOff>0</rowOff>
@@ -633,7 +633,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>26</row>
       <rowOff>0</rowOff>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -708,7 +708,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>37</row>
       <rowOff>0</rowOff>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -758,7 +758,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>40</row>
       <rowOff>0</rowOff>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,10 +810,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,10 +960,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1085,10 +1085,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1110,7 +1110,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1135,7 +1135,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1160,7 +1160,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1185,10 +1185,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="295275" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1210,7 +1210,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1235,7 +1235,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1260,10 +1260,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="295275" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1285,7 +1285,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1296,81 +1296,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1914,7 +1839,7 @@
     <row r="6" outlineLevel="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>数据更新：2026-07-12 · PoE2 0.5.4</t>
+          <t>数据更新：2026-07-16 · PoE2 0.5.4</t>
         </is>
       </c>
     </row>
@@ -2989,8 +2914,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>極盛 II
-(Zenith II)</t>
+          <t>Zenith II</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -3028,9 +2952,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能增加25%魔力消耗效率
-★ 你的魔力高於最大魔力的90%時，被輔助的法術造成30%更多傷害
-▶ 零魔力技能可满层 Zenith</t>
+          <t>▶ 零魔力技能可满层 Zenith</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -3791,30 +3713,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>林木塑像
-(Sylvan's Effigy)</t>
+          <t>Sylvan's Effigy</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="264" customHeight="1">
+    <row r="81" outlineLevel="1" ht="84" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>林木塑像 (Sylvan's Effigy)
-底材：Stoic Sceptre
-需求:  等級 62, 12 智慧
-■ 賦予技能: 紀律
-■ 賦予技能: 等級 14 阿茲莫里巨狼
-★ 增加(50—75)%精魂
-★ 處於你存在範圍中的友方每秒回復(50—100)生命
-★ +(6—12)點全部能力值
-★ 盟友對你標記的目標增加(50—100)%傷害
-★ 你可以擁有任意數量的不同類型盟友
-★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
-on hollow winds. The moon listens. The pack gathers.」
+          <t>Sylvan's Effigy
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3830,27 +3739,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>永恆火花
-(The Eternal Spark)</t>
+          <t>The Eternal Spark</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="216" customHeight="1">
+    <row r="84" outlineLevel="1" ht="84" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>永恆火花 (The Eternal Spark)
-底材：Crystal Focus
-需求:  等級 26, 38 智慧
-★ 增加(50—70)%能量護盾
-★ +5%最大閃電抗性
-★ +(20—30)%閃電抗性
-★ 增加40%魔力回復率
-★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
-her motionless dance the pulse of bliss」
+          <t>The Eternal Spark
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -5243,7 +5142,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未見之道</t>
+          <t>未见之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5256,11 +5155,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E57" s="5" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5520,7 +5415,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5533,11 +5428,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5547,7 +5438,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5560,11 +5451,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5574,7 +5461,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5587,11 +5474,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5677,7 +5560,7 @@
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（12/16 条）</t>
         </is>
       </c>
     </row>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,9 +333,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -358,9 +358,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -510,7 +510,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -535,7 +535,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -560,10 +560,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -585,7 +585,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -608,12 +608,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -633,12 +633,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -660,7 +660,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -708,12 +708,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -735,7 +735,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -758,9 +758,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -785,7 +785,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="609600"/>
@@ -835,7 +835,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,7 +910,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,10 +960,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="295275" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1085,7 +1085,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1096,206 +1096,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="295275" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2502,21 +2302,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>法術圖騰
-(Level)
+          <t>Spell Totem
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>恐怖之柱
-(Level)</t>
+          <t>Grim Pillars</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>苦澀衰亡
-(Level)</t>
+          <t>Bitter Dead</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2533,50 +2330,25 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>達拉的渴望
-(Date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1" ht="110" customHeight="1">
+          <t>Dialla's Desire</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="80" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>★ 圖騰持續時間為8秒
-★ 限制(1—2)個圖騰
-★ 圖騰獲得+(0—75)%全元素抗性
-★ 圖騰獲得+(0—35)%混沌抗性
-★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
-★ 每消耗1耐力球，召喚的圖騰有20%更多生命
-★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
-★ 插槽中的法術有25%更少施放速度
-▶ 图腾施法核心</t>
+          <t>▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>★ 造成(3—99)至(5—149)冰冷傷害
-★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
-★ 創造半徑為4公尺
-★ 創造8根恐怖之柱
-★ 噴發範圍為@1.2公尺
-★ 恐怖之柱持續10秒
-★ 恐怖之柱擁有(27—9536)最大生命
-★ 恐怖之柱上限為20根
-▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>★ 轉化半徑為3.5公尺
-★ 轉化至多(1—7)具屍體
-★ 核心持續時間為5秒
-★ 造成(9—319)至(14—478)冰冷傷害
-★ 爆炸範圍為2公尺
-★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
-★ 冰緩半徑1.5公尺內的敵人
-★ 法術傷害同時影響此技能的持續傷害減益效果
-▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2593,9 +2365,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>★ +5%被輔助的技能的品質
-★ 被輔助的技能寶石等級+1
-▶ 达拉血统辅助</t>
+          <t>▶ 达拉血统辅助</t>
         </is>
       </c>
     </row>
@@ -2684,8 +2454,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>大法師
-(Level)
+          <t>Archmage
 Lv.21</t>
         </is>
       </c>
@@ -2701,19 +2470,15 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>阿茲里的共融
-(Date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1" ht="84" customHeight="1">
+          <t>Atziri's Communion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="80" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
-★ 非引導法術額外消耗你最大魔力的(6.1—8)%
-★ base deal no damage 1
-▶ 法力转法术伤害</t>
+          <t>▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2728,8 +2493,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能會保留等同於66%基礎精魂保留的最大生命百分比
-▶ 插 Archmage</t>
+          <t>▶ 插 Archmage</t>
         </is>
       </c>
     </row>
@@ -2742,8 +2506,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>纏繞
-(Level)
+          <t>Entangle
 Lv.13</t>
         </is>
       </c>
@@ -2773,21 +2536,11 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
+    <row r="18" outlineLevel="1" ht="80" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
-■ 將技能「纏結」的特效替換為冥河。
-★ 造成(4—111)至(6—167)物理傷害
-★ 裂縫長度為8米
-★ 對1.5公尺內的敵人附加藤蔓
-★ 限制(4—8)道裂縫
-★ 裂縫持續時間為8秒
-★ 每0.1秒附加一條藤蔓
-★ 當過度生長時根鬚失效速度減緩25%
-★ 造成(1—29)至(1—43)物理傷害
-▶ 引爆冰柱清图</t>
+          <t>▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2825,8 +2578,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>瀆神
-(Level)
+          <t>Blasphemy
 Lv.18</t>
         </is>
       </c>
@@ -2856,20 +2608,11 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
+    <row r="21" outlineLevel="1" ht="80" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 插槽中的詛咒技能會以光環的形式影響周圍
-★ 每個插槽中的詛咒占用60精魂
-★ 被輔助的詛咒有(41—50)%更少效果幅度
-★ 插槽中的技能在基礎範圍上額外增加+1公尺
-★ base deal no damage 1
-▶ 诅咒光环</t>
+          <t>▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -3167,8 +2910,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>烏特雷的儀式
-(Date)</t>
+          <t>Uhtred's Rite</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -3199,10 +2941,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能使用時根據每1秒冷卻時間，獲得持續1秒的滿溢聖杯
-★ 被輔助的技能在任意生命藥劑作用期間內造成20%更多傷害
-★ 被輔助的技能在任意魔力藥劑作用期間內增加20%魔力消耗效率
-▶ 插 Refutation</t>
+          <t>▶ 插 Refutation</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -3242,8 +2981,7 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>卡塔爾的恢復
-(Date)</t>
+          <t>Khatal's Rejuvenation</t>
         </is>
       </c>
     </row>
@@ -3272,9 +3010,7 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助技能所創造的痕跡會在拾取時賦予卡塔爾的回春
-★ base_cooldown_speed_+%
-▶ 生命痕跡族裔辅助</t>
+          <t>▶ 生命痕跡族裔辅助</t>
         </is>
       </c>
     </row>
@@ -3713,17 +3449,30 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy</t>
+          <t>林木塑像
+(Sylvan's Effigy)</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="84" customHeight="1">
+    <row r="81" outlineLevel="1" ht="264" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy
+          <t>林木塑像 (Sylvan's Effigy)
+底材：Stoic Sceptre
+需求:  等級 62, 12 智慧
+■ 賦予技能: 紀律
+■ 賦予技能: 等級 14 阿茲莫里巨狼
+★ 增加(50—75)%精魂
+★ 處於你存在範圍中的友方每秒回復(50—100)生命
+★ +(6—12)點全部能力值
+★ 盟友對你標記的目標增加(50—100)%傷害
+★ 你可以擁有任意數量的不同類型盟友
+★ discipline art variation 1
+「Darkness howls through ancient bones, a wistful cry
+on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3739,17 +3488,27 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>The Eternal Spark</t>
+          <t>永恆火花
+(The Eternal Spark)</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="84" customHeight="1">
+    <row r="84" outlineLevel="1" ht="216" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Spark
+          <t>永恆火花 (The Eternal Spark)
+底材：Crystal Focus
+需求:  等級 26, 38 智慧
+★ 增加(50—70)%能量護盾
+★ +5%最大閃電抗性
+★ +(20—30)%閃電抗性
+★ 增加40%魔力回復率
+★ 站立時，增加40%魔力回復率
+「A flash of blue, a stormcloud's kiss,
+her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -5115,7 +4874,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虛實交織</t>
+          <t>虚实交织</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5128,11 +4887,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E56" s="5" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5165,7 +4920,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>無名心木</t>
+          <t>无名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -5178,11 +4933,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E58" s="5" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
@@ -5192,7 +4943,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>微小損害</t>
+          <t>微小损害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5205,11 +4956,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="5" t="inlineStr">
@@ -5273,7 +5020,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>對你的暴擊傷害加成</t>
+          <t>对你的暴击伤害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5286,11 +5033,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5388,7 +5131,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>同袍情誼</t>
+          <t>同袍情谊</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5401,11 +5144,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E67" s="5" t="inlineStr"/>
     </row>
     <row r="68" outlineLevel="1">
       <c r="A68" s="5" t="inlineStr">
@@ -5560,7 +5299,7 @@
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（12/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（7/16 条）</t>
         </is>
       </c>
     </row>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,9 +333,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -358,9 +358,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -510,7 +510,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -535,7 +535,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -560,10 +560,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -608,12 +608,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -635,10 +635,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -660,7 +660,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -683,9 +683,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,10 +710,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -735,7 +735,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,10 +760,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -785,7 +785,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,10 +810,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,7 +860,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -885,7 +885,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,7 +960,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="295275" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1085,7 +1085,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1096,6 +1096,131 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="295275" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1126,31 +1251,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2302,18 +2402,21 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Spell Totem
+          <t>法術圖騰
+(Level)
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Grim Pillars</t>
+          <t>恐怖之柱
+(Level)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bitter Dead</t>
+          <t>苦澀衰亡
+(Level)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2330,25 +2433,50 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Dialla's Desire</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1" ht="80" customHeight="1">
+          <t>達拉的渴望
+(Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="110" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>▶ 图腾施法核心</t>
+          <t>★ 圖騰持續時間為8秒
+★ 限制(1—2)個圖騰
+★ 圖騰獲得+(0—75)%全元素抗性
+★ 圖騰獲得+(0—35)%混沌抗性
+★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
+★ 每消耗1耐力球，召喚的圖騰有20%更多生命
+★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
+★ 插槽中的法術有25%更少施放速度
+▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>★ 造成(3—99)至(5—149)冰冷傷害
+★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
+★ 創造半徑為4公尺
+★ 創造8根恐怖之柱
+★ 噴發範圍為@1.2公尺
+★ 恐怖之柱持續10秒
+★ 恐怖之柱擁有(27—9536)最大生命
+★ 恐怖之柱上限為20根
+▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>★ 轉化半徑為3.5公尺
+★ 轉化至多(1—7)具屍體
+★ 核心持續時間為5秒
+★ 造成(9—319)至(14—478)冰冷傷害
+★ 爆炸範圍為2公尺
+★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
+★ 冰緩半徑1.5公尺內的敵人
+★ 法術傷害同時影響此技能的持續傷害減益效果
+▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2365,7 +2493,9 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>▶ 达拉血统辅助</t>
+          <t>★ +5%被輔助的技能的品質
+★ 被輔助的技能寶石等級+1
+▶ 达拉血统辅助</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2584,8 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Archmage
+          <t>大法師
+(Level)
 Lv.21</t>
         </is>
       </c>
@@ -2470,15 +2601,19 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Atziri's Communion</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1" ht="80" customHeight="1">
+          <t>阿茲里的共融
+(Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="84" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>▶ 法力转法术伤害</t>
+          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
+★ 非引導法術額外消耗你最大魔力的(6.1—8)%
+★ base deal no damage 1
+▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2493,7 +2628,8 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Archmage</t>
+          <t>★ 被輔助的技能會保留等同於66%基礎精魂保留的最大生命百分比
+▶ 插 Archmage</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2642,8 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Entangle
+          <t>纏繞
+(Level)
 Lv.13</t>
         </is>
       </c>
@@ -2536,11 +2673,21 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="80" customHeight="1">
+    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>▶ 引爆冰柱清图</t>
+          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
+■ 將技能「纏結」的特效替換為冥河。
+★ 造成(4—111)至(6—167)物理傷害
+★ 裂縫長度為8米
+★ 對1.5公尺內的敵人附加藤蔓
+★ 限制(4—8)道裂縫
+★ 裂縫持續時間為8秒
+★ 每0.1秒附加一條藤蔓
+★ 當過度生長時根鬚失效速度減緩25%
+★ 造成(1—29)至(1—43)物理傷害
+▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2578,7 +2725,8 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Blasphemy
+          <t>瀆神
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2608,11 +2756,20 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="80" customHeight="1">
+    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>▶ 诅咒光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 插槽中的詛咒技能會以光環的形式影響周圍
+★ 每個插槽中的詛咒占用60精魂
+★ 被輔助的詛咒有(41—50)%更少效果幅度
+★ 插槽中的技能在基礎範圍上額外增加+1公尺
+★ base deal no damage 1
+▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2723,8 +2880,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>閃電淨化
-(Level)
+          <t>Purity of Lightning
 Lv.18</t>
         </is>
       </c>
@@ -2746,18 +2902,11 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
+    <row r="27" outlineLevel="1" ht="80" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 光環賦予+(22—41)%閃電抗性
-★ base deal no damage 1
-★ skill desired amount override 1
-▶ 闪电抗性光环</t>
+          <t>▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2910,7 +3059,8 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Uhtred's Rite</t>
+          <t>烏特雷的儀式
+(Date)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2941,7 +3091,10 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Refutation</t>
+          <t>★ 被輔助的技能使用時根據每1秒冷卻時間，獲得持續1秒的滿溢聖杯
+★ 被輔助的技能在任意生命藥劑作用期間內造成20%更多傷害
+★ 被輔助的技能在任意魔力藥劑作用期間內增加20%魔力消耗效率
+▶ 插 Refutation</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -3449,30 +3602,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>林木塑像
-(Sylvan's Effigy)</t>
+          <t>Sylvan's Effigy</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="264" customHeight="1">
+    <row r="81" outlineLevel="1" ht="84" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>林木塑像 (Sylvan's Effigy)
-底材：Stoic Sceptre
-需求:  等級 62, 12 智慧
-■ 賦予技能: 紀律
-■ 賦予技能: 等級 14 阿茲莫里巨狼
-★ 增加(50—75)%精魂
-★ 處於你存在範圍中的友方每秒回復(50—100)生命
-★ +(6—12)點全部能力值
-★ 盟友對你標記的目標增加(50—100)%傷害
-★ 你可以擁有任意數量的不同類型盟友
-★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
-on hollow winds. The moon listens. The pack gathers.」
+          <t>Sylvan's Effigy
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3488,27 +3628,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>永恆火花
-(The Eternal Spark)</t>
+          <t>The Eternal Spark</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="216" customHeight="1">
+    <row r="84" outlineLevel="1" ht="84" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>永恆火花 (The Eternal Spark)
-底材：Crystal Focus
-需求:  等級 26, 38 智慧
-★ 增加(50—70)%能量護盾
-★ +5%最大閃電抗性
-★ +(20—30)%閃電抗性
-★ 增加40%魔力回復率
-★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
-her motionless dance the pulse of bliss」
+          <t>The Eternal Spark
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3830,21 +3960,17 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="108" customHeight="1">
+    <row r="116" outlineLevel="1" ht="60" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -4920,7 +5046,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>无名心木</t>
+          <t>無名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4933,7 +5059,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
@@ -5043,7 +5173,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>圖騰攻擊及施放速度</t>
+          <t>图腾施放和攻击速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5056,11 +5186,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5104,7 +5230,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算獵者</t>
+          <t>精算猎者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5117,11 +5243,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E66" s="5" t="inlineStr"/>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5131,7 +5253,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>同袍情谊</t>
+          <t>同袍情誼</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5144,7 +5266,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="68" outlineLevel="1">
       <c r="A68" s="5" t="inlineStr">
@@ -5223,7 +5349,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5236,11 +5362,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5250,7 +5372,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5263,11 +5385,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E72" s="5" t="inlineStr"/>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5277,7 +5395,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5290,16 +5408,12 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E73" s="5" t="inlineStr"/>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（7/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（4/16 条）</t>
         </is>
       </c>
     </row>
@@ -5841,21 +5955,17 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="132" customHeight="1">
+    <row r="106" outlineLevel="1" ht="84" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -585,7 +585,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -608,7 +608,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>26</row>
       <rowOff>0</rowOff>
@@ -633,9 +633,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -683,9 +683,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,10 +760,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,10 +810,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -835,7 +835,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="400050" cy="609600"/>
@@ -860,7 +860,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,7 +960,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1085,10 +1085,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1110,7 +1110,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1135,10 +1135,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="295275" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1160,7 +1160,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1185,7 +1185,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1210,7 +1210,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1221,6 +1221,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="295275" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1251,6 +1401,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2814,7 +2989,8 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Zenith II</t>
+          <t>極盛 II
+(Zenith II)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -2852,7 +3028,9 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>▶ 零魔力技能可满层 Zenith</t>
+          <t>★ 被輔助的技能增加25%魔力消耗效率
+★ 你的魔力高於最大魔力的90%時，被輔助的法術造成30%更多傷害
+▶ 零魔力技能可满层 Zenith</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -2880,7 +3058,8 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Purity of Lightning
+          <t>閃電淨化
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2902,11 +3081,18 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="80" customHeight="1">
+    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>▶ 闪电抗性光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 光環賦予+(22—41)%閃電抗性
+★ base deal no damage 1
+★ skill desired amount override 1
+▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -3134,7 +3320,8 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Khatal's Rejuvenation</t>
+          <t>卡塔爾的恢復
+(Date)</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3350,9 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>▶ 生命痕跡族裔辅助</t>
+          <t>★ 被輔助技能所創造的痕跡會在拾取時賦予卡塔爾的回春
+★ base_cooldown_speed_+%
+▶ 生命痕跡族裔辅助</t>
         </is>
       </c>
     </row>
@@ -3602,17 +3791,30 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy</t>
+          <t>林木塑像
+(Sylvan's Effigy)</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="84" customHeight="1">
+    <row r="81" outlineLevel="1" ht="264" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy
+          <t>林木塑像 (Sylvan's Effigy)
+底材：Stoic Sceptre
+需求:  等級 62, 12 智慧
+■ 賦予技能: 紀律
+■ 賦予技能: 等級 14 阿茲莫里巨狼
+★ 增加(50—75)%精魂
+★ 處於你存在範圍中的友方每秒回復(50—100)生命
+★ +(6—12)點全部能力值
+★ 盟友對你標記的目標增加(50—100)%傷害
+★ 你可以擁有任意數量的不同類型盟友
+★ discipline art variation 1
+「Darkness howls through ancient bones, a wistful cry
+on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3628,17 +3830,27 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>The Eternal Spark</t>
+          <t>永恆火花
+(The Eternal Spark)</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="84" customHeight="1">
+    <row r="84" outlineLevel="1" ht="216" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Spark
+          <t>永恆火花 (The Eternal Spark)
+底材：Crystal Focus
+需求:  等級 26, 38 智慧
+★ 增加(50—70)%能量護盾
+★ +5%最大閃電抗性
+★ +(20—30)%閃電抗性
+★ 增加40%魔力回復率
+★ 站立時，增加40%魔力回復率
+「A flash of blue, a stormcloud's kiss,
+her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3960,17 +4172,21 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="60" customHeight="1">
+    <row r="116" outlineLevel="1" ht="108" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -5000,7 +5216,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虚实交织</t>
+          <t>虛實交織</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5013,7 +5229,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5023,7 +5243,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未见之道</t>
+          <t>未見之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5036,7 +5256,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5073,7 +5297,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>微小损害</t>
+          <t>微小損害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5086,7 +5310,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="5" t="inlineStr">
@@ -5150,7 +5378,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>对你的暴击伤害加成</t>
+          <t>對你的暴擊傷害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5163,7 +5391,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5173,7 +5405,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>图腾施放和攻击速度</t>
+          <t>圖騰攻擊及施放速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5186,7 +5418,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5230,7 +5466,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算猎者</t>
+          <t>精算獵者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5243,7 +5479,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5280,7 +5520,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5293,7 +5533,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5303,7 +5547,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5316,7 +5560,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5326,7 +5574,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5339,7 +5587,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5349,7 +5601,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5362,7 +5614,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5372,7 +5628,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5385,7 +5641,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5395,7 +5655,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5408,12 +5668,16 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（4/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
         </is>
       </c>
     </row>
@@ -5955,17 +6219,21 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="84" customHeight="1">
+    <row r="106" outlineLevel="1" ht="132" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,7 +333,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -360,7 +360,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,10 +460,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -510,10 +510,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -535,10 +535,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -560,7 +560,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,10 +610,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -633,9 +633,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="295275" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,7 +860,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -921,456 +921,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="304800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="400050" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="295275" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1401,31 +951,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2577,21 +2102,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>法術圖騰
-(Level)
+          <t>Spell Totem
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>恐怖之柱
-(Level)</t>
+          <t>Grim Pillars</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>苦澀衰亡
-(Level)</t>
+          <t>Bitter Dead</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2613,45 +2135,21 @@
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1" ht="110" customHeight="1">
+    <row r="7" outlineLevel="1" ht="80" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>★ 圖騰持續時間為8秒
-★ 限制(1—2)個圖騰
-★ 圖騰獲得+(0—75)%全元素抗性
-★ 圖騰獲得+(0—35)%混沌抗性
-★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
-★ 每消耗1耐力球，召喚的圖騰有20%更多生命
-★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
-★ 插槽中的法術有25%更少施放速度
-▶ 图腾施法核心</t>
+          <t>▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>★ 造成(3—99)至(5—149)冰冷傷害
-★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
-★ 創造半徑為4公尺
-★ 創造8根恐怖之柱
-★ 噴發範圍為@1.2公尺
-★ 恐怖之柱持續10秒
-★ 恐怖之柱擁有(27—9536)最大生命
-★ 恐怖之柱上限為20根
-▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>★ 轉化半徑為3.5公尺
-★ 轉化至多(1—7)具屍體
-★ 核心持續時間為5秒
-★ 造成(9—319)至(14—478)冰冷傷害
-★ 爆炸範圍為2公尺
-★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
-★ 冰緩半徑1.5公尺內的敵人
-★ 法術傷害同時影響此技能的持續傷害減益效果
-▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2689,8 +2187,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>活體引爆
-(Level)</t>
+          <t>Detonate Living</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2699,7 +2196,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="110" customHeight="1">
+    <row r="10" outlineLevel="1" ht="80" customHeight="1">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="13" t="inlineStr">
         <is>
@@ -2708,15 +2205,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>★ 造成(1—30)至(2—46)物理傷害
-★ 撲殺
-★ 造成(28—177)至(42—265)物理傷害
-★ 造成等同於屍體最大生命(6.6—14.2)%的物理傷害
-★ 爆炸範圍為2.6公尺
-★ active skill show cull range 1
-★ can perform skill while moving 1
-★ movement speed +% final while performing action -70
-▶ Spellslinger 触发清图</t>
+          <t>▶ Spellslinger 触发清图</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -2759,8 +2248,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>大法師
-(Level)
+          <t>Archmage
 Lv.21</t>
         </is>
       </c>
@@ -2781,14 +2269,11 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="84" customHeight="1">
+    <row r="15" outlineLevel="1" ht="80" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
-★ 非引導法術額外消耗你最大魔力的(6.1—8)%
-★ base deal no damage 1
-▶ 法力转法术伤害</t>
+          <t>▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2817,8 +2302,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>纏繞
-(Level)
+          <t>Entangle
 Lv.13</t>
         </is>
       </c>
@@ -2848,21 +2332,11 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
+    <row r="18" outlineLevel="1" ht="80" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
-■ 將技能「纏結」的特效替換為冥河。
-★ 造成(4—111)至(6—167)物理傷害
-★ 裂縫長度為8米
-★ 對1.5公尺內的敵人附加藤蔓
-★ 限制(4—8)道裂縫
-★ 裂縫持續時間為8秒
-★ 每0.1秒附加一條藤蔓
-★ 當過度生長時根鬚失效速度減緩25%
-★ 造成(1—29)至(1—43)物理傷害
-▶ 引爆冰柱清图</t>
+          <t>▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2900,8 +2374,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>瀆神
-(Level)
+          <t>Blasphemy
 Lv.18</t>
         </is>
       </c>
@@ -2931,20 +2404,11 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
+    <row r="21" outlineLevel="1" ht="80" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 插槽中的詛咒技能會以光環的形式影響周圍
-★ 每個插槽中的詛咒占用60精魂
-★ 被輔助的詛咒有(41—50)%更少效果幅度
-★ 插槽中的技能在基礎範圍上額外增加+1公尺
-★ base deal no damage 1
-▶ 诅咒光环</t>
+          <t>▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2982,8 +2446,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>極地裝甲
-(Level)
+          <t>Arctic Armour
 Lv.19</t>
         </is>
       </c>
@@ -3009,21 +2472,11 @@
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="120.4" customHeight="1">
+    <row r="24" outlineLevel="1" ht="80" customHeight="1">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 將技能「極地裝甲」的特效替換為下著冰雹的雷雲。
-★ 每層造成(3—101)至(5—152)冰冷傷害
-★ 施加之冰緩具有100%更多幅度
-★ 100%更多冰凍累積
-★ 每(0.73—1.25)秒獲得1層，最多可達(2—5)層
-★ base_movement_velocity_+%
-★ mana_degeneration_per_minute
-★ physical_damage_taken_+
-★ fire_damage_taken_+
-▶ 冰霜防御</t>
+          <t>▶ 冰霜防御</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -3058,21 +2511,18 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>閃電淨化
-(Level)
+          <t>Purity of Lightning
 Lv.18</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>她的宣告
-(Date)</t>
+          <t>Her Declaration</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>神使之心
-(Date)</t>
+          <t>Seraph's Heart</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -3081,30 +2531,21 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
+    <row r="27" outlineLevel="1" ht="80" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 光環賦予+(22—41)%閃電抗性
-★ base deal no damage 1
-★ skill desired amount override 1
-▶ 闪电抗性光环</t>
+          <t>▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>★ 當被輔助的技能啟用時，進入你存在範圍內的敵人會被威嚇，持續4秒
-▶ 插 Purity of Lightning</t>
+          <t>▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>★ 當被輔助的技能啟用時，敵人的擊中有20%機率視你所有的抗性為90%
-▶ 插 Purity of Lightning</t>
+          <t>▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -3164,8 +2605,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>魔力痕跡
-(Level)
+          <t>Mana Remnants
 Lv.18</t>
         </is>
       </c>
@@ -3180,17 +2620,11 @@
         </is>
       </c>
     </row>
-    <row r="33" outlineLevel="1" ht="99.59999999999999" customHeight="1">
+    <row r="33" outlineLevel="1" ht="80" customHeight="1">
       <c r="A33" s="12" t="n"/>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>★ 痕跡持續8秒
-★ 擊殺受元素異常狀態影響的敵人時，有25%機率產生一道痕跡
-★ 對受元素異常狀態影響的目標造成暴擊時，產生一道痕跡，每2秒只能觸發一次
-★ 每個痕跡賦予(28—281)魔力
-★ base deal no damage 1
-★ mana_regeneration_rate_+%
-▶ 法力遗迹</t>
+          <t>▶ 法力遗迹</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3238,8 +2672,7 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>駁斥
-(Level)
+          <t>Refutation
 Lv.18</t>
         </is>
       </c>
@@ -3260,19 +2693,11 @@
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="1" ht="110" customHeight="1">
+    <row r="38" outlineLevel="1" ht="84" customHeight="1">
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>★ 冷卻時間在增益效果期間不會恢復
-★ 當增益效果作用期間，會被動的朝所有方向格擋且為被格擋的敵人施加受招架
-★ 增益效果持續時間為4秒
-★ 增益啟用期間擁有50%更少暈眩門檻
-★ 增益啟用期間，每消耗10符文保護即擁有5%更多暈眩門檻
-★ 受招架減益效果使目標承受50%更多攻擊傷害
-★ 受招架減益效果持續時間為(2—3.9)秒
-★ base deal no damage 1
-▶ Uhtred 辅助法术</t>
+          <t>▶ Uhtred 辅助法术</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -3303,8 +2728,7 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>卡爾葛之痕
-(Level)
+          <t>Remnants of Kalguur
 Lv.20</t>
         </is>
       </c>
@@ -3325,17 +2749,11 @@
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="99.59999999999999" customHeight="1">
+    <row r="41" outlineLevel="1" ht="80" customHeight="1">
       <c r="A41" s="12" t="n"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>★ 痕跡持續8秒
-★ 暈眩一名敵人時生成一個痕跡，每秒不超過一次
-★ 擊殺一名敵人時有25%機率生成一個痕跡
-★ 每個痕跡都會賦予(5—205)符文保護
-★ base deal no damage 1
-★ base deal no damage over time 1
-▶ 卡古尔遗迹</t>
+          <t>▶ 卡古尔遗迹</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -3365,8 +2783,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>元素匯流
-(Level)
+          <t>Elemental Conflux
 Lv.20</t>
         </is>
       </c>
@@ -3381,18 +2798,11 @@
         </is>
       </c>
     </row>
-    <row r="44" outlineLevel="1" ht="104.8" customHeight="1">
+    <row r="44" outlineLevel="1" ht="80" customHeight="1">
       <c r="A44" s="12" t="n"/>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-★ 元素隨機化的間隔時間為8秒
-★ 增益效果賦予(40—59)%更多受影響的元素傷害
-★ base deal no damage 1
-★ base_chance_to_ignite_%
-★ base_chance_to_shock_%
-★ all_damage_can_chill_ignite_shock
-▶ 元素汇聚</t>
+          <t>▶ 元素汇聚</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -3791,30 +3201,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>林木塑像
-(Sylvan's Effigy)</t>
+          <t>Sylvan's Effigy</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="264" customHeight="1">
+    <row r="81" outlineLevel="1" ht="84" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>林木塑像 (Sylvan's Effigy)
-底材：Stoic Sceptre
-需求:  等級 62, 12 智慧
-■ 賦予技能: 紀律
-■ 賦予技能: 等級 14 阿茲莫里巨狼
-★ 增加(50—75)%精魂
-★ 處於你存在範圍中的友方每秒回復(50—100)生命
-★ +(6—12)點全部能力值
-★ 盟友對你標記的目標增加(50—100)%傷害
-★ 你可以擁有任意數量的不同類型盟友
-★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
-on hollow winds. The moon listens. The pack gathers.」
+          <t>Sylvan's Effigy
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3830,27 +3227,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>永恆火花
-(The Eternal Spark)</t>
+          <t>The Eternal Spark</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="216" customHeight="1">
+    <row r="84" outlineLevel="1" ht="84" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>永恆火花 (The Eternal Spark)
-底材：Crystal Focus
-需求:  等級 26, 38 智慧
-★ 增加(50—70)%能量護盾
-★ +5%最大閃電抗性
-★ +(20—30)%閃電抗性
-★ 增加40%魔力回復率
-★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
-her motionless dance the pulse of bliss」
+          <t>The Eternal Spark
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -4172,21 +3559,17 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="108" customHeight="1">
+    <row r="116" outlineLevel="1" ht="60" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -5216,7 +4599,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虛實交織</t>
+          <t>虚实交织</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5229,11 +4612,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E56" s="5" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5243,7 +4622,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未見之道</t>
+          <t>未见之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5256,11 +4635,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E57" s="5" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5270,7 +4645,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>無名心木</t>
+          <t>无名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -5283,11 +4658,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E58" s="5" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
@@ -5297,7 +4668,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>微小損害</t>
+          <t>微小损害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5310,11 +4681,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="5" t="inlineStr">
@@ -5378,7 +4745,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>對你的暴擊傷害加成</t>
+          <t>对你的暴击伤害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5391,11 +4758,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5405,7 +4768,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>圖騰攻擊及施放速度</t>
+          <t>图腾施放和攻击速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5418,11 +4781,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5466,7 +4825,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算獵者</t>
+          <t>精算猎者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5479,11 +4838,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E66" s="5" t="inlineStr"/>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5493,7 +4848,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>同袍情誼</t>
+          <t>同袍情谊</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5506,11 +4861,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E67" s="5" t="inlineStr"/>
     </row>
     <row r="68" outlineLevel="1">
       <c r="A68" s="5" t="inlineStr">
@@ -5520,7 +4871,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5533,11 +4884,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5547,7 +4894,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5560,11 +4907,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5574,7 +4917,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5587,11 +4930,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5601,7 +4940,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5614,11 +4953,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5628,7 +4963,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5641,11 +4976,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E72" s="5" t="inlineStr"/>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5655,7 +4986,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5668,16 +4999,12 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E73" s="5" t="inlineStr"/>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（2/16 条）</t>
         </is>
       </c>
     </row>
@@ -6219,21 +5546,17 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="132" customHeight="1">
+    <row r="106" outlineLevel="1" ht="84" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,7 +333,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -360,7 +360,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,10 +460,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -510,10 +510,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -535,10 +535,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -560,7 +560,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,10 +610,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -633,9 +633,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="295275" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,7 +860,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -921,6 +921,456 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="295275" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -951,6 +1401,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2102,18 +2577,21 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Spell Totem
+          <t>法術圖騰
+(Level)
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Grim Pillars</t>
+          <t>恐怖之柱
+(Level)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bitter Dead</t>
+          <t>苦澀衰亡
+(Level)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2135,21 +2613,45 @@
         </is>
       </c>
     </row>
-    <row r="7" outlineLevel="1" ht="80" customHeight="1">
+    <row r="7" outlineLevel="1" ht="110" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>▶ 图腾施法核心</t>
+          <t>★ 圖騰持續時間為8秒
+★ 限制(1—2)個圖騰
+★ 圖騰獲得+(0—75)%全元素抗性
+★ 圖騰獲得+(0—35)%混沌抗性
+★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
+★ 每消耗1耐力球，召喚的圖騰有20%更多生命
+★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
+★ 插槽中的法術有25%更少施放速度
+▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>★ 造成(3—99)至(5—149)冰冷傷害
+★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
+★ 創造半徑為4公尺
+★ 創造8根恐怖之柱
+★ 噴發範圍為@1.2公尺
+★ 恐怖之柱持續10秒
+★ 恐怖之柱擁有(27—9536)最大生命
+★ 恐怖之柱上限為20根
+▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>★ 轉化半徑為3.5公尺
+★ 轉化至多(1—7)具屍體
+★ 核心持續時間為5秒
+★ 造成(9—319)至(14—478)冰冷傷害
+★ 爆炸範圍為2公尺
+★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
+★ 冰緩半徑1.5公尺內的敵人
+★ 法術傷害同時影響此技能的持續傷害減益效果
+▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2187,7 +2689,8 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Detonate Living</t>
+          <t>活體引爆
+(Level)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2196,7 +2699,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="80" customHeight="1">
+    <row r="10" outlineLevel="1" ht="110" customHeight="1">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="13" t="inlineStr">
         <is>
@@ -2205,7 +2708,15 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>▶ Spellslinger 触发清图</t>
+          <t>★ 造成(1—30)至(2—46)物理傷害
+★ 撲殺
+★ 造成(28—177)至(42—265)物理傷害
+★ 造成等同於屍體最大生命(6.6—14.2)%的物理傷害
+★ 爆炸範圍為2.6公尺
+★ active skill show cull range 1
+★ can perform skill while moving 1
+★ movement speed +% final while performing action -70
+▶ Spellslinger 触发清图</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -2248,7 +2759,8 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Archmage
+          <t>大法師
+(Level)
 Lv.21</t>
         </is>
       </c>
@@ -2269,11 +2781,14 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="80" customHeight="1">
+    <row r="15" outlineLevel="1" ht="84" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>▶ 法力转法术伤害</t>
+          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
+★ 非引導法術額外消耗你最大魔力的(6.1—8)%
+★ base deal no damage 1
+▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2302,7 +2817,8 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Entangle
+          <t>纏繞
+(Level)
 Lv.13</t>
         </is>
       </c>
@@ -2332,11 +2848,21 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="80" customHeight="1">
+    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>▶ 引爆冰柱清图</t>
+          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
+■ 將技能「纏結」的特效替換為冥河。
+★ 造成(4—111)至(6—167)物理傷害
+★ 裂縫長度為8米
+★ 對1.5公尺內的敵人附加藤蔓
+★ 限制(4—8)道裂縫
+★ 裂縫持續時間為8秒
+★ 每0.1秒附加一條藤蔓
+★ 當過度生長時根鬚失效速度減緩25%
+★ 造成(1—29)至(1—43)物理傷害
+▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2374,7 +2900,8 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Blasphemy
+          <t>瀆神
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2404,11 +2931,20 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="80" customHeight="1">
+    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>▶ 诅咒光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 插槽中的詛咒技能會以光環的形式影響周圍
+★ 每個插槽中的詛咒占用60精魂
+★ 被輔助的詛咒有(41—50)%更少效果幅度
+★ 插槽中的技能在基礎範圍上額外增加+1公尺
+★ base deal no damage 1
+▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2446,7 +2982,8 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Arctic Armour
+          <t>極地裝甲
+(Level)
 Lv.19</t>
         </is>
       </c>
@@ -2472,11 +3009,21 @@
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="80" customHeight="1">
+    <row r="24" outlineLevel="1" ht="120.4" customHeight="1">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>▶ 冰霜防御</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 將技能「極地裝甲」的特效替換為下著冰雹的雷雲。
+★ 每層造成(3—101)至(5—152)冰冷傷害
+★ 施加之冰緩具有100%更多幅度
+★ 100%更多冰凍累積
+★ 每(0.73—1.25)秒獲得1層，最多可達(2—5)層
+★ base_movement_velocity_+%
+★ mana_degeneration_per_minute
+★ physical_damage_taken_+
+★ fire_damage_taken_+
+▶ 冰霜防御</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -2511,18 +3058,21 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Purity of Lightning
+          <t>閃電淨化
+(Level)
 Lv.18</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Her Declaration</t>
+          <t>她的宣告
+(Date)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Seraph's Heart</t>
+          <t>神使之心
+(Date)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2531,21 +3081,30 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="80" customHeight="1">
+    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>▶ 闪电抗性光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 光環賦予+(22—41)%閃電抗性
+★ base deal no damage 1
+★ skill desired amount override 1
+▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Purity of Lightning</t>
+          <t>★ 當被輔助的技能啟用時，進入你存在範圍內的敵人會被威嚇，持續4秒
+▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Purity of Lightning</t>
+          <t>★ 當被輔助的技能啟用時，敵人的擊中有20%機率視你所有的抗性為90%
+▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2605,7 +3164,8 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Mana Remnants
+          <t>魔力痕跡
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2620,11 +3180,17 @@
         </is>
       </c>
     </row>
-    <row r="33" outlineLevel="1" ht="80" customHeight="1">
+    <row r="33" outlineLevel="1" ht="99.59999999999999" customHeight="1">
       <c r="A33" s="12" t="n"/>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>▶ 法力遗迹</t>
+          <t>★ 痕跡持續8秒
+★ 擊殺受元素異常狀態影響的敵人時，有25%機率產生一道痕跡
+★ 對受元素異常狀態影響的目標造成暴擊時，產生一道痕跡，每2秒只能觸發一次
+★ 每個痕跡賦予(28—281)魔力
+★ base deal no damage 1
+★ mana_regeneration_rate_+%
+▶ 法力遗迹</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -2672,7 +3238,8 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Refutation
+          <t>駁斥
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2693,11 +3260,19 @@
         </is>
       </c>
     </row>
-    <row r="38" outlineLevel="1" ht="84" customHeight="1">
+    <row r="38" outlineLevel="1" ht="110" customHeight="1">
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>▶ Uhtred 辅助法术</t>
+          <t>★ 冷卻時間在增益效果期間不會恢復
+★ 當增益效果作用期間，會被動的朝所有方向格擋且為被格擋的敵人施加受招架
+★ 增益效果持續時間為4秒
+★ 增益啟用期間擁有50%更少暈眩門檻
+★ 增益啟用期間，每消耗10符文保護即擁有5%更多暈眩門檻
+★ 受招架減益效果使目標承受50%更多攻擊傷害
+★ 受招架減益效果持續時間為(2—3.9)秒
+★ base deal no damage 1
+▶ Uhtred 辅助法术</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -2728,7 +3303,8 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Remnants of Kalguur
+          <t>卡爾葛之痕
+(Level)
 Lv.20</t>
         </is>
       </c>
@@ -2749,11 +3325,17 @@
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="80" customHeight="1">
+    <row r="41" outlineLevel="1" ht="99.59999999999999" customHeight="1">
       <c r="A41" s="12" t="n"/>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>▶ 卡古尔遗迹</t>
+          <t>★ 痕跡持續8秒
+★ 暈眩一名敵人時生成一個痕跡，每秒不超過一次
+★ 擊殺一名敵人時有25%機率生成一個痕跡
+★ 每個痕跡都會賦予(5—205)符文保護
+★ base deal no damage 1
+★ base deal no damage over time 1
+▶ 卡古尔遗迹</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -2783,7 +3365,8 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Elemental Conflux
+          <t>元素匯流
+(Level)
 Lv.20</t>
         </is>
       </c>
@@ -2798,11 +3381,18 @@
         </is>
       </c>
     </row>
-    <row r="44" outlineLevel="1" ht="80" customHeight="1">
+    <row r="44" outlineLevel="1" ht="104.8" customHeight="1">
       <c r="A44" s="12" t="n"/>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>▶ 元素汇聚</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+★ 元素隨機化的間隔時間為8秒
+★ 增益效果賦予(40—59)%更多受影響的元素傷害
+★ base deal no damage 1
+★ base_chance_to_ignite_%
+★ base_chance_to_shock_%
+★ all_damage_can_chill_ignite_shock
+▶ 元素汇聚</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -3201,17 +3791,30 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy</t>
+          <t>林木塑像
+(Sylvan's Effigy)</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="84" customHeight="1">
+    <row r="81" outlineLevel="1" ht="264" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy
+          <t>林木塑像 (Sylvan's Effigy)
+底材：Stoic Sceptre
+需求:  等級 62, 12 智慧
+■ 賦予技能: 紀律
+■ 賦予技能: 等級 14 阿茲莫里巨狼
+★ 增加(50—75)%精魂
+★ 處於你存在範圍中的友方每秒回復(50—100)生命
+★ +(6—12)點全部能力值
+★ 盟友對你標記的目標增加(50—100)%傷害
+★ 你可以擁有任意數量的不同類型盟友
+★ discipline art variation 1
+「Darkness howls through ancient bones, a wistful cry
+on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3227,17 +3830,27 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>The Eternal Spark</t>
+          <t>永恆火花
+(The Eternal Spark)</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="84" customHeight="1">
+    <row r="84" outlineLevel="1" ht="216" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Spark
+          <t>永恆火花 (The Eternal Spark)
+底材：Crystal Focus
+需求:  等級 26, 38 智慧
+★ 增加(50—70)%能量護盾
+★ +5%最大閃電抗性
+★ +(20—30)%閃電抗性
+★ 增加40%魔力回復率
+★ 站立時，增加40%魔力回復率
+「A flash of blue, a stormcloud's kiss,
+her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3559,17 +4172,21 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="60" customHeight="1">
+    <row r="116" outlineLevel="1" ht="108" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -5546,17 +6163,21 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="84" customHeight="1">
+    <row r="106" outlineLevel="1" ht="132" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虚实交织</t>
+          <t>虛實交織</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5229,7 +5229,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5239,7 +5243,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未见之道</t>
+          <t>未見之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5252,7 +5256,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5262,7 +5270,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>无名心木</t>
+          <t>無名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -5275,7 +5283,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
@@ -5285,7 +5297,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>微小损害</t>
+          <t>微小損害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5298,7 +5310,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="5" t="inlineStr">
@@ -5362,7 +5378,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>对你的暴击伤害加成</t>
+          <t>對你的暴擊傷害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5375,7 +5391,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5385,7 +5405,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>图腾施放和攻击速度</t>
+          <t>圖騰攻擊及施放速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5398,7 +5418,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5442,7 +5466,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算猎者</t>
+          <t>精算獵者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5455,7 +5479,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5465,7 +5493,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>同袍情谊</t>
+          <t>同袍情誼</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5478,7 +5506,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="68" outlineLevel="1">
       <c r="A68" s="5" t="inlineStr">
@@ -5488,7 +5520,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5501,7 +5533,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5511,7 +5547,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5524,7 +5560,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5534,7 +5574,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5547,7 +5587,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5557,7 +5601,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5570,7 +5614,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5580,7 +5628,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5593,7 +5641,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5603,7 +5655,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5616,12 +5668,16 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（2/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
         </is>
       </c>
     </row>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,9 +333,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -358,9 +358,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,12 +483,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -510,7 +510,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -535,10 +535,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -560,10 +560,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,7 +610,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -633,12 +633,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="295275" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -946,431 +946,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="304800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>72</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="400050" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="295275" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1401,31 +976,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2577,21 +2127,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>法術圖騰
-(Level)
+          <t>Spell Totem
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>恐怖之柱
-(Level)</t>
+          <t>Grim Pillars</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>苦澀衰亡
-(Level)</t>
+          <t>Bitter Dead</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2608,50 +2155,25 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>達拉的渴望
-(Date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1" ht="110" customHeight="1">
+          <t>Dialla's Desire</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="80" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>★ 圖騰持續時間為8秒
-★ 限制(1—2)個圖騰
-★ 圖騰獲得+(0—75)%全元素抗性
-★ 圖騰獲得+(0—35)%混沌抗性
-★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
-★ 每消耗1耐力球，召喚的圖騰有20%更多生命
-★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
-★ 插槽中的法術有25%更少施放速度
-▶ 图腾施法核心</t>
+          <t>▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>★ 造成(3—99)至(5—149)冰冷傷害
-★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
-★ 創造半徑為4公尺
-★ 創造8根恐怖之柱
-★ 噴發範圍為@1.2公尺
-★ 恐怖之柱持續10秒
-★ 恐怖之柱擁有(27—9536)最大生命
-★ 恐怖之柱上限為20根
-▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>★ 轉化半徑為3.5公尺
-★ 轉化至多(1—7)具屍體
-★ 核心持續時間為5秒
-★ 造成(9—319)至(14—478)冰冷傷害
-★ 爆炸範圍為2公尺
-★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
-★ 冰緩半徑1.5公尺內的敵人
-★ 法術傷害同時影響此技能的持續傷害減益效果
-▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2668,9 +2190,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>★ +5%被輔助的技能的品質
-★ 被輔助的技能寶石等級+1
-▶ 达拉血统辅助</t>
+          <t>▶ 达拉血统辅助</t>
         </is>
       </c>
     </row>
@@ -2759,8 +2279,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>大法師
-(Level)
+          <t>Archmage
 Lv.21</t>
         </is>
       </c>
@@ -2776,19 +2295,15 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>阿茲里的共融
-(Date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1" ht="84" customHeight="1">
+          <t>Atziri's Communion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="80" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
-★ 非引導法術額外消耗你最大魔力的(6.1—8)%
-★ base deal no damage 1
-▶ 法力转法术伤害</t>
+          <t>▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2803,8 +2318,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能會保留等同於66%基礎精魂保留的最大生命百分比
-▶ 插 Archmage</t>
+          <t>▶ 插 Archmage</t>
         </is>
       </c>
     </row>
@@ -2817,8 +2331,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>纏繞
-(Level)
+          <t>Entangle
 Lv.13</t>
         </is>
       </c>
@@ -2848,21 +2361,11 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
+    <row r="18" outlineLevel="1" ht="80" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
-■ 將技能「纏結」的特效替換為冥河。
-★ 造成(4—111)至(6—167)物理傷害
-★ 裂縫長度為8米
-★ 對1.5公尺內的敵人附加藤蔓
-★ 限制(4—8)道裂縫
-★ 裂縫持續時間為8秒
-★ 每0.1秒附加一條藤蔓
-★ 當過度生長時根鬚失效速度減緩25%
-★ 造成(1—29)至(1—43)物理傷害
-▶ 引爆冰柱清图</t>
+          <t>▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2900,8 +2403,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>瀆神
-(Level)
+          <t>Blasphemy
 Lv.18</t>
         </is>
       </c>
@@ -2931,20 +2433,11 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
+    <row r="21" outlineLevel="1" ht="80" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 插槽中的詛咒技能會以光環的形式影響周圍
-★ 每個插槽中的詛咒占用60精魂
-★ 被輔助的詛咒有(41—50)%更少效果幅度
-★ 插槽中的技能在基礎範圍上額外增加+1公尺
-★ base deal no damage 1
-▶ 诅咒光环</t>
+          <t>▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2982,15 +2475,13 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>極地裝甲
-(Level)
+          <t>Arctic Armour
 Lv.19</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>極盛 II
-(Zenith II)</t>
+          <t>Zenith II</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -3009,28 +2500,16 @@
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="120.4" customHeight="1">
+    <row r="24" outlineLevel="1" ht="80" customHeight="1">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 將技能「極地裝甲」的特效替換為下著冰雹的雷雲。
-★ 每層造成(3—101)至(5—152)冰冷傷害
-★ 施加之冰緩具有100%更多幅度
-★ 100%更多冰凍累積
-★ 每(0.73—1.25)秒獲得1層，最多可達(2—5)層
-★ base_movement_velocity_+%
-★ mana_degeneration_per_minute
-★ physical_damage_taken_+
-★ fire_damage_taken_+
-▶ 冰霜防御</t>
+          <t>▶ 冰霜防御</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能增加25%魔力消耗效率
-★ 你的魔力高於最大魔力的90%時，被輔助的法術造成30%更多傷害
-▶ 零魔力技能可满层 Zenith</t>
+          <t>▶ 零魔力技能可满层 Zenith</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -3065,14 +2544,12 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>她的宣告
-(Date)</t>
+          <t>Her Declaration</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>神使之心
-(Date)</t>
+          <t>Seraph's Heart</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -3097,14 +2574,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>★ 當被輔助的技能啟用時，進入你存在範圍內的敵人會被威嚇，持續4秒
-▶ 插 Purity of Lightning</t>
+          <t>▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>★ 當被輔助的技能啟用時，敵人的擊中有20%機率視你所有的抗性為90%
-▶ 插 Purity of Lightning</t>
+          <t>▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -3245,8 +2720,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>烏特雷的儀式
-(Date)</t>
+          <t>Uhtred's Rite</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -3277,10 +2751,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能使用時根據每1秒冷卻時間，獲得持續1秒的滿溢聖杯
-★ 被輔助的技能在任意生命藥劑作用期間內造成20%更多傷害
-★ 被輔助的技能在任意魔力藥劑作用期間內增加20%魔力消耗效率
-▶ 插 Refutation</t>
+          <t>▶ 插 Refutation</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -3320,8 +2791,7 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>卡塔爾的恢復
-(Date)</t>
+          <t>Khatal's Rejuvenation</t>
         </is>
       </c>
     </row>
@@ -3350,9 +2820,7 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助技能所創造的痕跡會在拾取時賦予卡塔爾的回春
-★ base_cooldown_speed_+%
-▶ 生命痕跡族裔辅助</t>
+          <t>▶ 生命痕跡族裔辅助</t>
         </is>
       </c>
     </row>
@@ -3791,30 +3259,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>林木塑像
-(Sylvan's Effigy)</t>
+          <t>Sylvan's Effigy</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="264" customHeight="1">
+    <row r="81" outlineLevel="1" ht="84" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>林木塑像 (Sylvan's Effigy)
-底材：Stoic Sceptre
-需求:  等級 62, 12 智慧
-■ 賦予技能: 紀律
-■ 賦予技能: 等級 14 阿茲莫里巨狼
-★ 增加(50—75)%精魂
-★ 處於你存在範圍中的友方每秒回復(50—100)生命
-★ +(6—12)點全部能力值
-★ 盟友對你標記的目標增加(50—100)%傷害
-★ 你可以擁有任意數量的不同類型盟友
-★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
-on hollow winds. The moon listens. The pack gathers.」
+          <t>Sylvan's Effigy
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3830,27 +3285,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>永恆火花
-(The Eternal Spark)</t>
+          <t>The Eternal Spark</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="216" customHeight="1">
+    <row r="84" outlineLevel="1" ht="84" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>永恆火花 (The Eternal Spark)
-底材：Crystal Focus
-需求:  等級 26, 38 智慧
-★ 增加(50—70)%能量護盾
-★ +5%最大閃電抗性
-★ +(20—30)%閃電抗性
-★ 增加40%魔力回復率
-★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
-her motionless dance the pulse of bliss」
+          <t>The Eternal Spark
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -4172,21 +3617,17 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="108" customHeight="1">
+    <row r="116" outlineLevel="1" ht="60" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -5216,7 +4657,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虛實交織</t>
+          <t>虚实交织</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5229,11 +4670,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E56" s="5" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -5243,7 +4680,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未見之道</t>
+          <t>未见之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5256,11 +4693,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E57" s="5" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5378,7 +4811,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>對你的暴擊傷害加成</t>
+          <t>对你的暴击伤害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5391,11 +4824,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -5405,7 +4834,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>圖騰攻擊及施放速度</t>
+          <t>图腾施放和攻击速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5418,11 +4847,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5466,7 +4891,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算獵者</t>
+          <t>精算猎者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5479,11 +4904,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E66" s="5" t="inlineStr"/>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -5520,7 +4941,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5533,11 +4954,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5547,7 +4964,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5560,11 +4977,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5574,7 +4987,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5587,11 +5000,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5601,7 +5010,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5614,11 +5023,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5628,7 +5033,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5641,11 +5046,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E72" s="5" t="inlineStr"/>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5655,7 +5056,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5668,16 +5069,12 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E73" s="5" t="inlineStr"/>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（5/16 条）</t>
         </is>
       </c>
     </row>
@@ -6219,21 +5616,17 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="132" customHeight="1">
+    <row r="106" outlineLevel="1" ht="84" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -283,7 +283,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -308,7 +308,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -333,9 +333,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -358,9 +358,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,12 +483,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -510,7 +510,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -535,10 +535,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -560,10 +560,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,7 +610,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -633,12 +633,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -685,7 +685,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,7 +760,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -783,9 +783,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="295275" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -946,6 +946,431 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="295275" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -976,6 +1401,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2127,18 +2577,21 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Spell Totem
+          <t>法術圖騰
+(Level)
 Lv.7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Grim Pillars</t>
+          <t>恐怖之柱
+(Level)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Bitter Dead</t>
+          <t>苦澀衰亡
+(Level)</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -2155,25 +2608,50 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Dialla's Desire</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1" ht="80" customHeight="1">
+          <t>達拉的渴望
+(Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="110" customHeight="1">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>▶ 图腾施法核心</t>
+          <t>★ 圖騰持續時間為8秒
+★ 限制(1—2)個圖騰
+★ 圖騰獲得+(0—75)%全元素抗性
+★ 圖騰獲得+(0—35)%混沌抗性
+★ 每消耗1暴擊球插槽中的技能造成10%更多傷害
+★ 每消耗1耐力球，召喚的圖騰有20%更多生命
+★ 每消耗1耐力球，召喚的圖騰有20%更多持續時間
+★ 插槽中的法術有25%更少施放速度
+▶ 图腾施法核心</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
+          <t>★ 造成(3—99)至(5—149)冰冷傷害
+★ 如果在0.5秒內被不是你的其他來源破壞，造成80%更少傷害
+★ 創造半徑為4公尺
+★ 創造8根恐怖之柱
+★ 噴發範圍為@1.2公尺
+★ 恐怖之柱持續10秒
+★ 恐怖之柱擁有(27—9536)最大生命
+★ 恐怖之柱上限為20根
+▶ BD 主伤害：铺冰柱，图腾施放免 Ward</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>▶ 插图腾链：尸体冰霜 DoT</t>
+          <t>★ 轉化半徑為3.5公尺
+★ 轉化至多(1—7)具屍體
+★ 核心持續時間為5秒
+★ 造成(9—319)至(14—478)冰冷傷害
+★ 爆炸範圍為2公尺
+★ 冰緩視同對敵人造成(26—888)至(39—1332)冰冷傷害
+★ 冰緩半徑1.5公尺內的敵人
+★ 法術傷害同時影響此技能的持續傷害減益效果
+▶ 插图腾链：尸体冰霜 DoT</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -2190,7 +2668,9 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>▶ 达拉血统辅助</t>
+          <t>★ +5%被輔助的技能的品質
+★ 被輔助的技能寶石等級+1
+▶ 达拉血统辅助</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2759,8 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Archmage
+          <t>大法師
+(Level)
 Lv.21</t>
         </is>
       </c>
@@ -2295,15 +2776,19 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Atziri's Communion</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" outlineLevel="1" ht="80" customHeight="1">
+          <t>阿茲里的共融
+(Date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="84" customHeight="1">
       <c r="A15" s="12" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>▶ 法力转法术伤害</t>
+          <t>★ 你每擁有100最大魔力，非引導法術獲得等同於4%傷害的額外閃電傷害
+★ 非引導法術額外消耗你最大魔力的(6.1—8)%
+★ base deal no damage 1
+▶ 法力转法术伤害</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -2318,7 +2803,8 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Archmage</t>
+          <t>★ 被輔助的技能會保留等同於66%基礎精魂保留的最大生命百分比
+▶ 插 Archmage</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2817,8 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Entangle
+          <t>纏繞
+(Level)
 Lv.13</t>
         </is>
       </c>
@@ -2361,11 +2848,21 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="80" customHeight="1">
+    <row r="18" outlineLevel="1" ht="120.4" customHeight="1">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>▶ 引爆冰柱清图</t>
+          <t>■ 將技能「纏結」的特效替換為獸性奔騰。
+■ 將技能「纏結」的特效替換為冥河。
+★ 造成(4—111)至(6—167)物理傷害
+★ 裂縫長度為8米
+★ 對1.5公尺內的敵人附加藤蔓
+★ 限制(4—8)道裂縫
+★ 裂縫持續時間為8秒
+★ 每0.1秒附加一條藤蔓
+★ 當過度生長時根鬚失效速度減緩25%
+★ 造成(1—29)至(1—43)物理傷害
+▶ 引爆冰柱清图</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -2403,7 +2900,8 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Blasphemy
+          <t>瀆神
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2433,11 +2931,20 @@
         </is>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="80" customHeight="1">
+    <row r="21" outlineLevel="1" ht="115.2" customHeight="1">
       <c r="A21" s="12" t="n"/>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>▶ 诅咒光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 插槽中的詛咒技能會以光環的形式影響周圍
+★ 每個插槽中的詛咒占用60精魂
+★ 被輔助的詛咒有(41—50)%更少效果幅度
+★ 插槽中的技能在基礎範圍上額外增加+1公尺
+★ base deal no damage 1
+▶ 诅咒光环</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -2475,13 +2982,15 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Arctic Armour
+          <t>極地裝甲
+(Level)
 Lv.19</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Zenith II</t>
+          <t>極盛 II
+(Zenith II)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -2500,16 +3009,28 @@
         </is>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="80" customHeight="1">
+    <row r="24" outlineLevel="1" ht="120.4" customHeight="1">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>▶ 冰霜防御</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 將技能「極地裝甲」的特效替換為下著冰雹的雷雲。
+★ 每層造成(3—101)至(5—152)冰冷傷害
+★ 施加之冰緩具有100%更多幅度
+★ 100%更多冰凍累積
+★ 每(0.73—1.25)秒獲得1層，最多可達(2—5)層
+★ base_movement_velocity_+%
+★ mana_degeneration_per_minute
+★ physical_damage_taken_+
+★ fire_damage_taken_+
+▶ 冰霜防御</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>▶ 零魔力技能可满层 Zenith</t>
+          <t>★ 被輔助的技能增加25%魔力消耗效率
+★ 你的魔力高於最大魔力的90%時，被輔助的法術造成30%更多傷害
+▶ 零魔力技能可满层 Zenith</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -2544,12 +3065,14 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Her Declaration</t>
+          <t>她的宣告
+(Date)</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Seraph's Heart</t>
+          <t>神使之心
+(Date)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2574,12 +3097,14 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Purity of Lightning</t>
+          <t>★ 當被輔助的技能啟用時，進入你存在範圍內的敵人會被威嚇，持續4秒
+▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Purity of Lightning</t>
+          <t>★ 當被輔助的技能啟用時，敵人的擊中有20%機率視你所有的抗性為90%
+▶ 插 Purity of Lightning</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2720,7 +3245,8 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Uhtred's Rite</t>
+          <t>烏特雷的儀式
+(Date)</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2751,7 +3277,10 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>▶ 插 Refutation</t>
+          <t>★ 被輔助的技能使用時根據每1秒冷卻時間，獲得持續1秒的滿溢聖杯
+★ 被輔助的技能在任意生命藥劑作用期間內造成20%更多傷害
+★ 被輔助的技能在任意魔力藥劑作用期間內增加20%魔力消耗效率
+▶ 插 Refutation</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -2791,7 +3320,8 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Khatal's Rejuvenation</t>
+          <t>卡塔爾的恢復
+(Date)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +3350,9 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>▶ 生命痕跡族裔辅助</t>
+          <t>★ 被輔助技能所創造的痕跡會在拾取時賦予卡塔爾的回春
+★ base_cooldown_speed_+%
+▶ 生命痕跡族裔辅助</t>
         </is>
       </c>
     </row>
@@ -3259,17 +3791,30 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy</t>
+          <t>林木塑像
+(Sylvan's Effigy)</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="84" customHeight="1">
+    <row r="81" outlineLevel="1" ht="264" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy
+          <t>林木塑像 (Sylvan's Effigy)
+底材：Stoic Sceptre
+需求:  等級 62, 12 智慧
+■ 賦予技能: 紀律
+■ 賦予技能: 等級 14 阿茲莫里巨狼
+★ 增加(50—75)%精魂
+★ 處於你存在範圍中的友方每秒回復(50—100)生命
+★ +(6—12)點全部能力值
+★ 盟友對你標記的目標增加(50—100)%傷害
+★ 你可以擁有任意數量的不同類型盟友
+★ discipline art variation 1
+「Darkness howls through ancient bones, a wistful cry
+on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3285,17 +3830,27 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>The Eternal Spark</t>
+          <t>永恆火花
+(The Eternal Spark)</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="84" customHeight="1">
+    <row r="84" outlineLevel="1" ht="216" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Spark
+          <t>永恆火花 (The Eternal Spark)
+底材：Crystal Focus
+需求:  等級 26, 38 智慧
+★ 增加(50—70)%能量護盾
+★ +5%最大閃電抗性
+★ +(20—30)%閃電抗性
+★ 增加40%魔力回復率
+★ 站立時，增加40%魔力回復率
+「A flash of blue, a stormcloud's kiss,
+her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3617,17 +4172,21 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="60" customHeight="1">
+    <row r="116" outlineLevel="1" ht="108" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -4657,7 +5216,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虚实交织</t>
+          <t>虛實交織</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4670,7 +5229,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -4680,7 +5243,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未见之道</t>
+          <t>未見之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4693,7 +5256,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -4811,7 +5378,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>对你的暴击伤害加成</t>
+          <t>對你的暴擊傷害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4824,7 +5391,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -4834,7 +5405,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>图腾施放和攻击速度</t>
+          <t>圖騰攻擊及施放速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -4847,7 +5418,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4891,7 +5466,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算猎者</t>
+          <t>精算獵者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -4904,7 +5479,11 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="5" t="inlineStr">
@@ -4941,7 +5520,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -4954,7 +5533,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -4964,7 +5547,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4977,7 +5560,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr"/>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -4987,7 +5574,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>暴擊傷害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5000,7 +5587,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5010,7 +5601,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5023,7 +5614,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="72" outlineLevel="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5033,7 +5628,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5046,7 +5641,11 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="73" outlineLevel="1">
       <c r="A73" s="5" t="inlineStr">
@@ -5056,7 +5655,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>伤害与召唤物伤害</t>
+          <t>傷害和召喚物傷害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5069,12 +5668,16 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>✓poe2db</t>
+        </is>
+      </c>
     </row>
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（5/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
         </is>
       </c>
     </row>
@@ -5616,17 +6219,21 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="84" customHeight="1">
+    <row r="106" outlineLevel="1" ht="132" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -358,7 +358,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -508,9 +508,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -533,9 +533,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -558,9 +558,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,7 +610,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -635,7 +635,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -683,9 +683,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,10 +760,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -783,12 +783,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,7 +960,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1071,306 +1071,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="400050" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>83</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="295275" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>112</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1401,31 +1101,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="609600" cy="609600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2596,14 +2271,12 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>烏特雷的占卜術
-(Date)</t>
+          <t>Uhtred's Augury</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>萊基亞塔的流動
-(Date)</t>
+          <t>Rakiata's Flow</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -2656,14 +2329,12 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>★ 如果被輔助的技能恰好被兩顆輔助寶石修改，其等級+2
-▶ 恰好 2 辅助时 +2 技能等级，插图腾链</t>
+          <t>▶ 恰好 2 辅助时 +2 技能等级，插图腾链</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>★ 被輔助的技能擊中會將敵對怪物的元素抗性數值視為顛倒
-▶ 冰霜伤害辅助，插 Grim Pillars</t>
+          <t>▶ 冰霜伤害辅助，插 Grim Pillars</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -2689,8 +2360,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>活體引爆
-(Level)</t>
+          <t>Detonate Living</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2699,7 +2369,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="110" customHeight="1">
+    <row r="10" outlineLevel="1" ht="80" customHeight="1">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="13" t="inlineStr">
         <is>
@@ -2708,15 +2378,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>★ 造成(1—30)至(2—46)物理傷害
-★ 撲殺
-★ 造成(28—177)至(42—265)物理傷害
-★ 造成等同於屍體最大生命(6.6—14.2)%的物理傷害
-★ 爆炸範圍為2.6公尺
-★ active skill show cull range 1
-★ can perform skill while moving 1
-★ movement speed +% final while performing action -70
-▶ Spellslinger 触发清图</t>
+          <t>▶ Spellslinger 触发清图</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -3058,8 +2720,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>閃電淨化
-(Level)
+          <t>Purity of Lightning
 Lv.18</t>
         </is>
       </c>
@@ -3081,18 +2742,11 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
+    <row r="27" outlineLevel="1" ht="80" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
-■ 你的光環特效替換為力場防護罩。
-■ 你的光環特效替換為一個閃耀著電光的骷髏。
-■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
-★ 光環賦予+(22—41)%閃電抗性
-★ base deal no damage 1
-★ skill desired amount override 1
-▶ 闪电抗性光环</t>
+          <t>▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -3439,29 +3093,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>祖靈之約
-(Soul Mantle)</t>
+          <t>Soul Mantle</t>
         </is>
       </c>
       <c r="C48" s="15" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" ht="240" customHeight="1">
+    <row r="49" outlineLevel="1" ht="84" customHeight="1">
       <c r="A49" s="12" t="n"/>
       <c r="B49" s="13" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>祖靈之約 (Soul Mantle)
-底材：Sacrificial Mantle
-需求:  等級 36, 33 力量, 33 智慧
-★ 增加(80—120)%護甲值和能量護盾
-★ +75精魂
-★ +10點力量
-★ +15點智慧
-★ +1召喚圖騰最大數量
-★ 當你的圖騰死亡時，會對你施加一個隨機的詛咒，並無視詛咒數量上限
-★ 減少(20—30)%圖騰生命
-「The greatest mistakes cause suffering
-long after they have been made」
+          <t>Soul Mantle
 ▶ BD 用途：BD核心：自诅咒 +1 图腾。突变词缀 20% 图腾伤害/诅咒
 🔗 https://poe2db.tw/tw/Soul_Mantle
 ▶ Runemastered；符文 -50% 诅咒效果 + Bonded 诅咒幅度</t>
@@ -3537,31 +3179,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>引導之掌：靈
-(Guiding Palm of the Mind)</t>
+          <t>Guiding Palm of the Mind</t>
         </is>
       </c>
       <c r="C57" s="15" t="n"/>
     </row>
-    <row r="58" outlineLevel="1" ht="276" customHeight="1">
+    <row r="58" outlineLevel="1" ht="84" customHeight="1">
       <c r="A58" s="12" t="n"/>
       <c r="B58" s="13" t="inlineStr"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>引導之掌：靈 (Guiding Palm of the Mind)
-底材：Shrine Sceptre
-需求:  等級 65, 17 力量, 38 智慧
-■ 賦予技能: 閃電淨化
-★ 獲得等同於傷害25%的額外閃電傷害
-★ 處於你存在範圍中的友方造成1至(56—70)額外攻擊閃電傷害
-★ 賦予存在範圍內的友方你自身50%的基礎生命回復
-★ +(20—30)點敏捷
-★ 增加25%光線範圍
-★ 賦予引導暴風神殿的效果
-「"Deep in thought, you would tremble the very air before you.
-Wreathed in light, you nurtured them all. 
-And yet... Your nature became you."
-The Dreamer mused with aching heart, as remnants of forking tendrils burst forth.」
+          <t>Guiding Palm of the Mind
 ▶ BD 用途：副手权杖：Spirit 光环 + 闪电伤害
 🔗 https://poe2db.tw/tw/Guiding_Palm_of_the_Mind
 ▶ Guided Tempest Shrine</t>
@@ -3607,22 +3235,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>卡蘭德之觸
-(Kalandra's Touch)</t>
+          <t>Kalandra's Touch</t>
         </is>
       </c>
       <c r="C63" s="15" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" ht="156" customHeight="1">
+    <row r="64" outlineLevel="1" ht="84" customHeight="1">
       <c r="A64" s="12" t="n"/>
       <c r="B64" s="13" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>卡蘭德之觸 (Kalandra's Touch)
-底材：Ring
-需求:  等級 1
-★ 複製對側戒指效果
-「Power is a matter of perspective.」
+          <t>Kalandra's Touch
 ▶ BD 用途：镜像戒指机制，与另一枚戒指配对
 🔗 https://poe2db.tw/tw/Kalandras_Touch
 ▶ 镜像戒</t>
@@ -3699,31 +3322,17 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>夜鱗
-(Nightscale)</t>
+          <t>Nightscale</t>
         </is>
       </c>
       <c r="C72" s="15" t="n"/>
     </row>
-    <row r="73" outlineLevel="1" ht="276" customHeight="1">
+    <row r="73" outlineLevel="1" ht="84" customHeight="1">
       <c r="A73" s="12" t="n"/>
       <c r="B73" s="13" t="inlineStr"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>夜鱗 (Nightscale)
-底材：Pauascale Gloves
-需求:  等級 45, 56 智慧
-■ local hand wraps player level to use 0
-■ 每一玩家等級+3閃避值每一玩家等級+1最大能量護盾local level requirement override 1
-★ 增加(60—100)%能量護盾
-★ 增加(30—50)%暴擊率
-★ +(10—20)點智慧
-★ +(20—30)%冰冷抗性
-★ 若你近期造成暴擊，增加150%魔力回復率
-★ 若你近期未造成暴擊，無法回復魔力
-★ (15—25)%更多全域閃避值和能量護盾
-★ 增加(40—60)%暴擊率
-「Diamora sings not for hunger, but for longing.」
+          <t>Nightscale
 ▶ BD 用途：100% ES 手套，暴击向
 🔗 https://poe2db.tw/tw/Nightscale
 ▶ Runemastered</t>
@@ -3791,30 +3400,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>林木塑像
-(Sylvan's Effigy)</t>
+          <t>Sylvan's Effigy</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="264" customHeight="1">
+    <row r="81" outlineLevel="1" ht="84" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>林木塑像 (Sylvan's Effigy)
-底材：Stoic Sceptre
-需求:  等級 62, 12 智慧
-■ 賦予技能: 紀律
-■ 賦予技能: 等級 14 阿茲莫里巨狼
-★ 增加(50—75)%精魂
-★ 處於你存在範圍中的友方每秒回復(50—100)生命
-★ +(6—12)點全部能力值
-★ 盟友對你標記的目標增加(50—100)%傷害
-★ 你可以擁有任意數量的不同類型盟友
-★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
-on hollow winds. The moon listens. The pack gathers.」
+          <t>Sylvan's Effigy
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3830,27 +3426,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>永恆火花
-(The Eternal Spark)</t>
+          <t>The Eternal Spark</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="216" customHeight="1">
+    <row r="84" outlineLevel="1" ht="84" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>永恆火花 (The Eternal Spark)
-底材：Crystal Focus
-需求:  等級 26, 38 智慧
-★ 增加(50—70)%能量護盾
-★ +5%最大閃電抗性
-★ +(20—30)%閃電抗性
-★ 增加40%魔力回復率
-★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
-her motionless dance the pulse of bliss」
+          <t>The Eternal Spark
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3890,23 +3476,17 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>妄想症
-(Megalomaniac)</t>
+          <t>Megalomaniac</t>
         </is>
       </c>
       <c r="C88" s="15" t="n"/>
     </row>
-    <row r="89" outlineLevel="1" ht="144" customHeight="1">
+    <row r="89" outlineLevel="1" ht="76" customHeight="1">
       <c r="A89" s="12" t="n"/>
       <c r="B89" s="13" t="inlineStr"/>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>妄想症 (Megalomaniac)
-底材：Diamond
-需求:  等級 20
-★ 配置Passive Skill
-「If you're going to act like you're better
-than everyone else, make sure you are.」
+          <t>Megalomaniac
 ▶ BD 用途：可选基石珠宝
 🔗 https://poe2db.tw/tw/Megalomaniac</t>
         </is>
@@ -3921,24 +3501,17 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>水井之心
-(Heart of the Well)</t>
+          <t>Heart of the Well</t>
         </is>
       </c>
       <c r="C91" s="15" t="n"/>
     </row>
-    <row r="92" outlineLevel="1" ht="156" customHeight="1">
+    <row r="92" outlineLevel="1" ht="76" customHeight="1">
       <c r="A92" s="12" t="n"/>
       <c r="B92" s="13" t="inlineStr"/>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>水井之心 (Heart of the Well)
-底材：Diamond
-需求:  等級 20
-★ Custom Desecrated prefix
-★ Custom Desecrated suffix
-「Countless souls scream in agonising harmony,
-forever sinking under the weight of the newly dead.」
+          <t>Heart of the Well
 ▶ BD 用途：井心珠宝，强力天赋加成
 🔗 https://poe2db.tw/tw/Heart_of_the_Well</t>
         </is>
@@ -4038,28 +3611,17 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>烏特雷的聖杯
-(Uhtred's Chalice)</t>
+          <t>Uhtred's Chalice</t>
         </is>
       </c>
       <c r="C103" s="15" t="n"/>
     </row>
-    <row r="104" outlineLevel="1" ht="204" customHeight="1">
+    <row r="104" outlineLevel="1" ht="60" customHeight="1">
       <c r="A104" s="12" t="n"/>
       <c r="B104" s="13" t="inlineStr"/>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>烏特雷的聖杯 (Uhtred's Chalice)
-底材：Transcendent Mana Flask
-需求:  等級 50
-★ 增加(200—300)%恢復量
-★ 減少70%恢復率
-★ 減少(50—60)%充能
-★ 效果期間內來自藥劑的魔力回復可以溢出最大魔力
-★ 效果期間內若你沒有符文保護，則每秒失去5%生命
-「Uhtred drank. Verisium burned through his veins.
-He gazed at death's face. With all his strength,
-he turned instead to the stars, and witnessed Truth.」
+          <t>Uhtred's Chalice
 ▶ BD 用途：卡古尔主题魔力药剂
 🔗 https://poe2db.tw/tw/Uhtreds_Chalice</t>
         </is>
@@ -4074,24 +3636,17 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>儀式通道
-(Rite of Passage)</t>
+          <t>Rite of Passage</t>
         </is>
       </c>
       <c r="C106" s="15" t="n"/>
     </row>
-    <row r="107" outlineLevel="1" ht="168" customHeight="1">
+    <row r="107" outlineLevel="1" ht="60" customHeight="1">
       <c r="A107" s="12" t="n"/>
       <c r="B107" s="13" t="inlineStr"/>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>儀式通道 (Rite of Passage)
-底材：Golden Charm
-需求:  等級 50
-■ 當你擊殺稀有或傳奇敵人時使用
-★ Possessed by Spirit Of The Azmeri Spirit for (10–20) seconds on use
-「To become a warrior and a hunter, each young
-Azmeri must prove themselves before the Spirit.」
+          <t>Rite of Passage
 ▶ BD 用途：金色护符，生存/机动
 🔗 https://poe2db.tw/tw/Rite_of_Passage</t>
         </is>
@@ -4106,25 +3661,17 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>黑貓
-(The Black Cat)</t>
+          <t>The Black Cat</t>
         </is>
       </c>
       <c r="C109" s="15" t="n"/>
     </row>
-    <row r="110" outlineLevel="1" ht="180" customHeight="1">
+    <row r="110" outlineLevel="1" ht="60" customHeight="1">
       <c r="A110" s="12" t="n"/>
       <c r="B110" s="13" t="inlineStr"/>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>黑貓 (The Black Cat)
-底材：Grounding Charm
-需求:  等級 32
-■ 當你被感電時使用
-★ 增加(10—20)%持續時間
-★ 在效果期間，敵人擊中你的閃電傷害相當不幸
-「The most beloved member of every Brinerot crew
-is the one that refuses to do any actual work.」
+          <t>The Black Cat
 ▶ BD 用途：接地护符，防闪电
 🔗 https://poe2db.tw/tw/The_Black_Cat</t>
         </is>
@@ -4139,25 +3686,17 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>斧頭之隕
-(The Fall of the Axe)</t>
+          <t>The Fall of the Axe</t>
         </is>
       </c>
       <c r="C112" s="15" t="n"/>
     </row>
-    <row r="113" outlineLevel="1" ht="180" customHeight="1">
+    <row r="113" outlineLevel="1" ht="60" customHeight="1">
       <c r="A113" s="12" t="n"/>
       <c r="B113" s="13" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>斧頭之隕 (The Fall of the Axe)
-底材：Silver Charm
-需求:  等級 10
-■ 當你受到緩速效果影響時使用
-★ 在效果期間賦予猛攻
-「"When the headsman's blade swings,
-your last moments stretch to eternity."
-- Vorm, the Twice-Pardoned」
+          <t>The Fall of the Axe
 ▶ BD 用途：银色护符
 🔗 https://poe2db.tw/tw/The_Fall_of_the_Axe</t>
         </is>
@@ -4172,21 +3711,17 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="108" customHeight="1">
+    <row r="116" outlineLevel="1" ht="60" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -5243,7 +4778,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>未見之道</t>
+          <t>未见之道</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5256,11 +4791,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E57" s="5" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5405,7 +4936,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>圖騰攻擊及施放速度</t>
+          <t>图腾施放和攻击速度</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5418,11 +4949,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -5520,7 +5047,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5533,11 +5060,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E68" s="5" t="inlineStr"/>
     </row>
     <row r="69" outlineLevel="1">
       <c r="A69" s="5" t="inlineStr">
@@ -5547,7 +5070,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5560,11 +5083,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E69" s="5" t="inlineStr"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5574,7 +5093,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>暴擊傷害</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5587,11 +5106,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E70" s="5" t="inlineStr"/>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="5" t="inlineStr">
@@ -5677,7 +5192,7 @@
     <row r="74" outlineLevel="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（16/16 条）</t>
+          <t>升华数据已与 poe2db.tw 交叉验证（11/16 条）</t>
         </is>
       </c>
     </row>
@@ -6219,21 +5734,17 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>守護神器
-(Warding Fetish)</t>
+          <t>Warding Fetish</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="132" customHeight="1">
+    <row r="106" outlineLevel="1" ht="84" customHeight="1">
       <c r="A106" s="12" t="n"/>
       <c r="B106" s="13" t="inlineStr"/>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>守護神器 (Warding Fetish)
-■ 你身上每有一個詛咒，增加30%傷害
-■ 減少30%你身上的詛咒效果
-■ 增加60%來自已裝備法器的能量護盾
+          <t>Warding Fetish
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -358,7 +358,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -383,9 +383,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -408,9 +408,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -433,9 +433,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -460,7 +460,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -483,9 +483,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -508,9 +508,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -533,9 +533,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -558,9 +558,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -583,9 +583,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -610,7 +610,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -635,7 +635,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -658,9 +658,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -683,9 +683,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -710,7 +710,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -733,9 +733,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -760,10 +760,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="200025" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -783,12 +783,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="400050" cy="609600"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -810,7 +810,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -835,10 +835,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -860,10 +860,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="304800"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -885,10 +885,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="200025" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -910,10 +910,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="400050" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -935,7 +935,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -960,7 +960,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -985,10 +985,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="609600" cy="609600"/>
+    <ext cx="609600" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -1010,7 +1010,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1035,7 +1035,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1060,7 +1060,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="609600" cy="609600"/>
@@ -1071,6 +1071,306 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="400050" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="295275" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1093,7 +1393,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6019800" cy="4476750"/>
+    <ext cx="4619625" cy="4476750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1101,6 +1401,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1582,14 +1907,14 @@
     <row r="5" outlineLevel="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>参考数据：Runes of Aldur · Lv.99 Oracle（poe.ninja 面板快照）</t>
+          <t>参考数据：Runes of Aldur · Lv.98 Oracle（poe.ninja 面板快照）</t>
         </is>
       </c>
     </row>
     <row r="6" outlineLevel="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>数据更新：2026-07-16 · PoE2 0.5.4</t>
+          <t>数据更新：2026-07-01 · PoE2 0.5.4</t>
         </is>
       </c>
     </row>
@@ -1775,7 +2100,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ninja 73% → 估算 75%</t>
+          <t>ninja 73%</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1792,7 +2117,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guiding Palm of the Mind 赋予 Purity of Lightning Lv.18 Q25：光环品质额外 +8% 闪电抗（ninja/PoB 面板常未计入）</t>
+          <t>ninja/PoB 面板闪电抗 73%：未计入权杖嵌入「闪电净化」技能品质对光环的抗性加成</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2129,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guiding Palm of the Mind 光环闪电抗 +40%（嵌入技能；面板抗性可能不含品质加成）</t>
+          <t>Guiding Palm 赋予 Purity of Lightning（权杖技能品质影响 +(0–8)% 闪电抗）</t>
         </is>
       </c>
     </row>
@@ -1816,7 +2141,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ninja 闪电抗 73%（未封顶）；II 组 Eternal Spark +30% 可补；权杖技能品质 +2% 可能是实际与面板差异来源</t>
+          <t>游戏内实际可能为 75% 封顶；II 组 Eternal Spark +30% 为另一补抗来源</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2596,14 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Uhtred's Augury</t>
+          <t>烏特雷的占卜術
+(Date)</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Rakiata's Flow</t>
+          <t>萊基亞塔的流動
+(Date)</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -2329,12 +2656,14 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>▶ 恰好 2 辅助时 +2 技能等级，插图腾链</t>
+          <t>★ 如果被輔助的技能恰好被兩顆輔助寶石修改，其等級+2
+▶ 恰好 2 辅助时 +2 技能等级，插图腾链</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>▶ 冰霜伤害辅助，插 Grim Pillars</t>
+          <t>★ 被輔助的技能擊中會將敵對怪物的元素抗性數值視為顛倒
+▶ 冰霜伤害辅助，插 Grim Pillars</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -2360,7 +2689,8 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Detonate Living</t>
+          <t>活體引爆
+(Level)</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2369,7 +2699,7 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="80" customHeight="1">
+    <row r="10" outlineLevel="1" ht="110" customHeight="1">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="13" t="inlineStr">
         <is>
@@ -2378,7 +2708,15 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>▶ Spellslinger 触发清图</t>
+          <t>★ 造成(1—30)至(2—46)物理傷害
+★ 撲殺
+★ 造成(28—177)至(42—265)物理傷害
+★ 造成等同於屍體最大生命(6.6—14.2)%的物理傷害
+★ 爆炸範圍為2.6公尺
+★ active skill show cull range 1
+★ can perform skill while moving 1
+★ movement speed +% final while performing action -70
+▶ Spellslinger 触发清图</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -2720,7 +3058,8 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Purity of Lightning
+          <t>閃電淨化
+(Level)
 Lv.18</t>
         </is>
       </c>
@@ -2733,7 +3072,7 @@
       <c r="D26" s="11" t="inlineStr">
         <is>
           <t>神使之心
-(Date)</t>
+(Seraph's Heart)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2742,11 +3081,18 @@
         </is>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="80" customHeight="1">
+    <row r="27" outlineLevel="1" ht="104.8" customHeight="1">
       <c r="A27" s="12" t="n"/>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>▶ 闪电抗性光环</t>
+          <t>■ 移除玩家極地裝甲、暴風之盾、鮮血狂怒、熔岩護盾、迷蹤、石化之血、光環、病疫之難、凋零之步、詛咒和捷光環的視覺特效。
+■ 你的光環特效替換為力場防護罩。
+■ 你的光環特效替換為一個閃耀著電光的骷髏。
+■ 你的光環特效替還為一個被地獄之火圍繞的骷髏。
+★ 光環賦予+(22—41)%閃電抗性
+★ base deal no damage 1
+★ skill desired amount override 1
+▶ 闪电抗性光环</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -3093,17 +3439,29 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Soul Mantle</t>
+          <t>祖靈之約
+(Soul Mantle)</t>
         </is>
       </c>
       <c r="C48" s="15" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" ht="84" customHeight="1">
+    <row r="49" outlineLevel="1" ht="240" customHeight="1">
       <c r="A49" s="12" t="n"/>
       <c r="B49" s="13" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Soul Mantle
+          <t>祖靈之約 (Soul Mantle)
+底材：Sacrificial Mantle
+需求:  等級 36, 33 力量, 33 智慧
+★ 增加(80—120)%護甲值和能量護盾
+★ +75精魂
+★ +10點力量
+★ +15點智慧
+★ +1召喚圖騰最大數量
+★ 當你的圖騰死亡時，會對你施加一個隨機的詛咒，並無視詛咒數量上限
+★ 減少(20—30)%圖騰生命
+「The greatest mistakes cause suffering
+long after they have been made」
 ▶ BD 用途：BD核心：自诅咒 +1 图腾。突变词缀 20% 图腾伤害/诅咒
 🔗 https://poe2db.tw/tw/Soul_Mantle
 ▶ Runemastered；符文 -50% 诅咒效果 + Bonded 诅咒幅度</t>
@@ -3179,17 +3537,31 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Guiding Palm of the Mind</t>
+          <t>引導之掌：靈
+(Guiding Palm of the Mind)</t>
         </is>
       </c>
       <c r="C57" s="15" t="n"/>
     </row>
-    <row r="58" outlineLevel="1" ht="84" customHeight="1">
+    <row r="58" outlineLevel="1" ht="276" customHeight="1">
       <c r="A58" s="12" t="n"/>
       <c r="B58" s="13" t="inlineStr"/>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Guiding Palm of the Mind
+          <t>引導之掌：靈 (Guiding Palm of the Mind)
+底材：Shrine Sceptre
+需求:  等級 65, 17 力量, 38 智慧
+■ 賦予技能: 閃電淨化
+★ 獲得等同於傷害25%的額外閃電傷害
+★ 處於你存在範圍中的友方造成1至(56—70)額外攻擊閃電傷害
+★ 賦予存在範圍內的友方你自身50%的基礎生命回復
+★ +(20—30)點敏捷
+★ 增加25%光線範圍
+★ 賦予引導暴風神殿的效果
+「"Deep in thought, you would tremble the very air before you.
+Wreathed in light, you nurtured them all. 
+And yet... Your nature became you."
+The Dreamer mused with aching heart, as remnants of forking tendrils burst forth.」
 ▶ BD 用途：副手权杖：Spirit 光环 + 闪电伤害
 🔗 https://poe2db.tw/tw/Guiding_Palm_of_the_Mind
 ▶ Guided Tempest Shrine</t>
@@ -3235,17 +3607,22 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Kalandra's Touch</t>
+          <t>卡蘭德之觸
+(Kalandra's Touch)</t>
         </is>
       </c>
       <c r="C63" s="15" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" ht="84" customHeight="1">
+    <row r="64" outlineLevel="1" ht="156" customHeight="1">
       <c r="A64" s="12" t="n"/>
       <c r="B64" s="13" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Kalandra's Touch
+          <t>卡蘭德之觸 (Kalandra's Touch)
+底材：Ring
+需求:  等級 1
+★ 複製對側戒指效果
+「Power is a matter of perspective.」
 ▶ BD 用途：镜像戒指机制，与另一枚戒指配对
 🔗 https://poe2db.tw/tw/Kalandras_Touch
 ▶ 镜像戒</t>
@@ -3322,17 +3699,31 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Nightscale</t>
+          <t>夜鱗
+(Nightscale)</t>
         </is>
       </c>
       <c r="C72" s="15" t="n"/>
     </row>
-    <row r="73" outlineLevel="1" ht="84" customHeight="1">
+    <row r="73" outlineLevel="1" ht="276" customHeight="1">
       <c r="A73" s="12" t="n"/>
       <c r="B73" s="13" t="inlineStr"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Nightscale
+          <t>夜鱗 (Nightscale)
+底材：Pauascale Gloves
+需求:  等級 45, 56 智慧
+■ local hand wraps player level to use 0
+■ 每一玩家等級+3閃避值每一玩家等級+1最大能量護盾local level requirement override 1
+★ 增加(60—100)%能量護盾
+★ 增加(30—50)%暴擊率
+★ +(10—20)點智慧
+★ +(20—30)%冰冷抗性
+★ 若你近期造成暴擊，增加150%魔力回復率
+★ 若你近期未造成暴擊，無法回復魔力
+★ (15—25)%更多全域閃避值和能量護盾
+★ 增加(40—60)%暴擊率
+「Diamora sings not for hunger, but for longing.」
 ▶ BD 用途：100% ES 手套，暴击向
 🔗 https://poe2db.tw/tw/Nightscale
 ▶ Runemastered</t>
@@ -3400,17 +3791,30 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy</t>
+          <t>林木塑像
+(Sylvan's Effigy)</t>
         </is>
       </c>
       <c r="C80" s="15" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" ht="84" customHeight="1">
+    <row r="81" outlineLevel="1" ht="264" customHeight="1">
       <c r="A81" s="12" t="n"/>
       <c r="B81" s="13" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Sylvan's Effigy
+          <t>林木塑像 (Sylvan's Effigy)
+底材：Stoic Sceptre
+需求:  等級 62, 12 智慧
+■ 賦予技能: 紀律
+■ 賦予技能: 等級 14 阿茲莫里巨狼
+★ 增加(50—75)%精魂
+★ 處於你存在範圍中的友方每秒回復(50—100)生命
+★ +(6—12)點全部能力值
+★ 盟友對你標記的目標增加(50—100)%傷害
+★ 你可以擁有任意數量的不同類型盟友
+★ discipline art variation 1
+「Darkness howls through ancient bones, a wistful cry
+on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
 ▶ +58% Spirit、+6 全属性，弥补 II 组无 Guiding Palm</t>
@@ -3426,17 +3830,27 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>The Eternal Spark</t>
+          <t>永恆火花
+(The Eternal Spark)</t>
         </is>
       </c>
       <c r="C83" s="15" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" ht="84" customHeight="1">
+    <row r="84" outlineLevel="1" ht="216" customHeight="1">
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>The Eternal Spark
+          <t>永恆火花 (The Eternal Spark)
+底材：Crystal Focus
+需求:  等級 26, 38 智慧
+★ 增加(50—70)%能量護盾
+★ +5%最大閃電抗性
+★ +(20—30)%閃電抗性
+★ 增加40%魔力回復率
+★ 站立時，增加40%魔力回復率
+「A flash of blue, a stormcloud's kiss,
+her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
 ▶ +30% 闪电抗、+5% 闪电抗上限，ES 向生存</t>
@@ -3476,17 +3890,23 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Megalomaniac</t>
+          <t>妄想症
+(Megalomaniac)</t>
         </is>
       </c>
       <c r="C88" s="15" t="n"/>
     </row>
-    <row r="89" outlineLevel="1" ht="76" customHeight="1">
+    <row r="89" outlineLevel="1" ht="144" customHeight="1">
       <c r="A89" s="12" t="n"/>
       <c r="B89" s="13" t="inlineStr"/>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Megalomaniac
+          <t>妄想症 (Megalomaniac)
+底材：Diamond
+需求:  等級 20
+★ 配置Passive Skill
+「If you're going to act like you're better
+than everyone else, make sure you are.」
 ▶ BD 用途：可选基石珠宝
 🔗 https://poe2db.tw/tw/Megalomaniac</t>
         </is>
@@ -3501,17 +3921,24 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Heart of the Well</t>
+          <t>水井之心
+(Heart of the Well)</t>
         </is>
       </c>
       <c r="C91" s="15" t="n"/>
     </row>
-    <row r="92" outlineLevel="1" ht="76" customHeight="1">
+    <row r="92" outlineLevel="1" ht="156" customHeight="1">
       <c r="A92" s="12" t="n"/>
       <c r="B92" s="13" t="inlineStr"/>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Heart of the Well
+          <t>水井之心 (Heart of the Well)
+底材：Diamond
+需求:  等級 20
+★ Custom Desecrated prefix
+★ Custom Desecrated suffix
+「Countless souls scream in agonising harmony,
+forever sinking under the weight of the newly dead.」
 ▶ BD 用途：井心珠宝，强力天赋加成
 🔗 https://poe2db.tw/tw/Heart_of_the_Well</t>
         </is>
@@ -3611,17 +4038,28 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Uhtred's Chalice</t>
+          <t>烏特雷的聖杯
+(Uhtred's Chalice)</t>
         </is>
       </c>
       <c r="C103" s="15" t="n"/>
     </row>
-    <row r="104" outlineLevel="1" ht="60" customHeight="1">
+    <row r="104" outlineLevel="1" ht="204" customHeight="1">
       <c r="A104" s="12" t="n"/>
       <c r="B104" s="13" t="inlineStr"/>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Uhtred's Chalice
+          <t>烏特雷的聖杯 (Uhtred's Chalice)
+底材：Transcendent Mana Flask
+需求:  等級 50
+★ 增加(200—300)%恢復量
+★ 減少70%恢復率
+★ 減少(50—60)%充能
+★ 效果期間內來自藥劑的魔力回復可以溢出最大魔力
+★ 效果期間內若你沒有符文保護，則每秒失去5%生命
+「Uhtred drank. Verisium burned through his veins.
+He gazed at death's face. With all his strength,
+he turned instead to the stars, and witnessed Truth.」
 ▶ BD 用途：卡古尔主题魔力药剂
 🔗 https://poe2db.tw/tw/Uhtreds_Chalice</t>
         </is>
@@ -3636,17 +4074,24 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>Rite of Passage</t>
+          <t>儀式通道
+(Rite of Passage)</t>
         </is>
       </c>
       <c r="C106" s="15" t="n"/>
     </row>
-    <row r="107" outlineLevel="1" ht="60" customHeight="1">
+    <row r="107" outlineLevel="1" ht="168" customHeight="1">
       <c r="A107" s="12" t="n"/>
       <c r="B107" s="13" t="inlineStr"/>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Rite of Passage
+          <t>儀式通道 (Rite of Passage)
+底材：Golden Charm
+需求:  等級 50
+■ 當你擊殺稀有或傳奇敵人時使用
+★ Possessed by Spirit Of The Azmeri Spirit for (10–20) seconds on use
+「To become a warrior and a hunter, each young
+Azmeri must prove themselves before the Spirit.」
 ▶ BD 用途：金色护符，生存/机动
 🔗 https://poe2db.tw/tw/Rite_of_Passage</t>
         </is>
@@ -3661,17 +4106,25 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>The Black Cat</t>
+          <t>黑貓
+(The Black Cat)</t>
         </is>
       </c>
       <c r="C109" s="15" t="n"/>
     </row>
-    <row r="110" outlineLevel="1" ht="60" customHeight="1">
+    <row r="110" outlineLevel="1" ht="180" customHeight="1">
       <c r="A110" s="12" t="n"/>
       <c r="B110" s="13" t="inlineStr"/>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>The Black Cat
+          <t>黑貓 (The Black Cat)
+底材：Grounding Charm
+需求:  等級 32
+■ 當你被感電時使用
+★ 增加(10—20)%持續時間
+★ 在效果期間，敵人擊中你的閃電傷害相當不幸
+「The most beloved member of every Brinerot crew
+is the one that refuses to do any actual work.」
 ▶ BD 用途：接地护符，防闪电
 🔗 https://poe2db.tw/tw/The_Black_Cat</t>
         </is>
@@ -3686,17 +4139,25 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>The Fall of the Axe</t>
+          <t>斧頭之隕
+(The Fall of the Axe)</t>
         </is>
       </c>
       <c r="C112" s="15" t="n"/>
     </row>
-    <row r="113" outlineLevel="1" ht="60" customHeight="1">
+    <row r="113" outlineLevel="1" ht="180" customHeight="1">
       <c r="A113" s="12" t="n"/>
       <c r="B113" s="13" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>The Fall of the Axe
+          <t>斧頭之隕 (The Fall of the Axe)
+底材：Silver Charm
+需求:  等級 10
+■ 當你受到緩速效果影響時使用
+★ 在效果期間賦予猛攻
+「"When the headsman's blade swings,
+your last moments stretch to eternity."
+- Vorm, the Twice-Pardoned」
 ▶ BD 用途：银色护符
 🔗 https://poe2db.tw/tw/The_Fall_of_the_Axe</t>
         </is>
@@ -3711,17 +4172,21 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Warding Fetish</t>
+          <t>守護神器
+(Warding Fetish)</t>
         </is>
       </c>
       <c r="C115" s="15" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="60" customHeight="1">
+    <row r="116" outlineLevel="1" ht="108" customHeight="1">
       <c r="A116" s="12" t="n"/>
       <c r="B116" s="13" t="inlineStr"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Warding Fetish
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish</t>
         </is>
@@ -3921,7 +4386,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>63（I组面板）</t>
+          <t>56（I组面板）</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -3938,7 +4403,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -3989,7 +4454,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>6,713</t>
+          <t>5,772</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -4195,7 +4660,7 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Str 仅 63+6，只能选低需求盾底</t>
+          <t>Str 仅 56+6，只能选低需求盾底</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4387,7 +4852,7 @@
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>图例：蓝 = 升华轮盘 · 浅蓝 = 未见之道 · 红 = 基石 · 黄 = notable · 灰 = 普通小点
-已点节点数：114（来源 poe.ninja passiveSelection）</t>
+已点节点数：0（来源 poe.ninja passiveSelection）</t>
         </is>
       </c>
     </row>
@@ -4751,7 +5216,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>虛實交織</t>
+          <t>虚实交织</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4764,11 +5229,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E56" s="5" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="1">
       <c r="A57" s="5" t="inlineStr">
@@ -4783,7 +5244,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>踏上未履之道；解锁先知专属天赋树分支</t>
+          <t>踏上未履之道；解锁「未见之道」专属天赋分支</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -4801,7 +5262,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>無名心木</t>
+          <t>无名心木</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4814,11 +5275,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E58" s="5" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="1">
       <c r="A59" s="5" t="inlineStr">
@@ -4828,7 +5285,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>微小損害</t>
+          <t>微小损害</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -4841,11 +5298,7 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="5" t="inlineStr">
@@ -4868,11 +5321,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E60" s="5" t="inlineStr"/>
     </row>
     <row r="61" outlineLevel="1">
       <c r="A61" s="5" t="inlineStr">
@@ -4895,11 +5344,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E61" s="5" t="inlineStr"/>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="5" t="inlineStr">
@@ -4909,7 +5354,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>對你的暴擊傷害加成</t>
+          <t>对你的暴击伤害加成</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -4922,11 +5367,7 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="5" t="inlineStr">
@@ -4985,7 +5426,7 @@
         </is>
       </c>
     </row>
-    <row r="66" outlineLevel="1">
+    <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>1</t>
@@ -4993,7 +5434,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>精算獵者</t>
+          <t>精算猎者</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5006,13 +5447,9 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
+      <c r="E66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>2</t>
@@ -5020,7 +5457,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>同袍情誼</t>
+          <t>同袍情谊</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5033,13 +5470,9 @@
           <t>升华核心</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" outlineLevel="1">
+      <c r="E67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>3</t>
@@ -5062,7 +5495,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr"/>
     </row>
-    <row r="69" outlineLevel="1">
+    <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>4</t>
@@ -5085,7 +5518,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr"/>
     </row>
-    <row r="70" outlineLevel="1">
+    <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>5</t>
@@ -5108,7 +5541,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr"/>
     </row>
-    <row r="71" outlineLevel="1">
+    <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>6</t>
@@ -5116,7 +5549,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5129,13 +5562,9 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" outlineLevel="1">
+      <c r="E71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>7</t>
@@ -5143,7 +5572,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5156,13 +5585,9 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" outlineLevel="1">
+      <c r="E72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>8</t>
@@ -5170,7 +5595,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>傷害和召喚物傷害</t>
+          <t>伤害与召唤物伤害</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5183,394 +5608,410 @@
           <t>升华小点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>✓poe2db</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>升华数据已与 poe2db.tw 交叉验证（11/16 条）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>▸ 武器组 I 天赋要点（24 点 · 伤害）</t>
         </is>
       </c>
     </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>优先词缀类</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
     <row r="76" outlineLevel="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>优先词缀类</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>冰霜 / 法术 / 暴击 / 图腾伤害</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Grim Pillars 主输出</t>
         </is>
       </c>
     </row>
     <row r="77" outlineLevel="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>图腾</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>冰霜 / 法术 / 暴击 / 图腾伤害</t>
+          <t>图腾数量、施放速度、生命</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Grim Pillars 主输出</t>
+          <t>配合 Ancestral Bond + Heartwood</t>
         </is>
       </c>
     </row>
     <row r="78" outlineLevel="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>图腾</t>
+          <t>诅咒</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>图腾数量、施放速度、生命</t>
+          <t>诅咒效果、额外诅咒槽</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>配合 Ancestral Bond + Heartwood</t>
+          <t>Blasphemy 链路</t>
         </is>
       </c>
     </row>
     <row r="79" outlineLevel="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>诅咒</t>
+          <t>法力</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>诅咒效果、额外诅咒槽</t>
+          <t>最大法力、回复、Archmage 协同</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Blasphemy 链路</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>法力</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>最大法力、回复、Archmage 协同</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
           <t>MoM + EB 第二血条</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>▸ 武器组 II 天赋要点（24 点 · 防御）</t>
         </is>
       </c>
     </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>优先词缀类</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
     <row r="82" outlineLevel="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>优先词缀类</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>护甲</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>护甲%、元素承伤转护甲</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>物承伤尖刺时切换</t>
         </is>
       </c>
     </row>
     <row r="83" outlineLevel="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>护甲</t>
+          <t>抗性</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>护甲%、元素承伤转护甲</t>
+          <t>全抗 / 闪电抗补满</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>物承伤尖刺时切换</t>
+          <t>配合 Eternal Spark +30%</t>
         </is>
       </c>
     </row>
     <row r="84" outlineLevel="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>抗性</t>
+          <t>格挡</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>全抗 / 闪电抗补满</t>
+          <t>格挡率与格挡效果</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>配合 Eternal Spark +30%</t>
+          <t>当前 0%，可选投资</t>
         </is>
       </c>
     </row>
     <row r="85" outlineLevel="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>格挡</t>
+          <t>法力</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>格挡率与格挡效果</t>
+          <t>保留与 Spirit 相关</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>当前 0%，可选投资</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" outlineLevel="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>法力</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>保留与 Spirit 相关</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
           <t>双勾技能不灰</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>▸ 加点顺序（待补充 · 占位模板）</t>
         </is>
       </c>
     </row>
+    <row r="87" outlineLevel="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>后续可按 PoB 导出或开荒录像填写具体节点名称与顺序。</t>
+        </is>
+      </c>
+    </row>
     <row r="88" outlineLevel="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>后续可按 PoB 导出或开荒录像填写具体节点名称与顺序。</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>天赋/节点</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="89" outlineLevel="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>阶段</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>天赋/节点</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>开荒</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>（待填）图腾 / 法术基础小点</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Act 1–2 清图与 Boss</t>
         </is>
       </c>
     </row>
     <row r="90" outlineLevel="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>开荒</t>
+          <t>中期</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>（待填）图腾 / 法术基础小点</t>
+          <t>（待填）Spell Totem + 诅咒链路</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Act 1–2 清图与 Boss</t>
+          <t>Bone Cage → Grim Pillars 转折</t>
         </is>
       </c>
     </row>
     <row r="91" outlineLevel="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>中期</t>
+          <t>成型</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>（待填）Spell Totem + 诅咒链路</t>
+          <t>（待填）MoM / EB / Archmage 路径</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Bone Cage → Grim Pillars 转折</t>
+          <t>法力池与低血 PA</t>
         </is>
       </c>
     </row>
     <row r="92" outlineLevel="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>成型</t>
+          <t>升华</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>（待填）MoM / EB / Archmage 路径</t>
+          <t>（待填）轮盘 8 点顺序</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>法力池与低血 PA</t>
+          <t>Entwined → Unseen Path → Heartwood…</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>升华</t>
+          <t>毕业</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>（待填）轮盘 8 点顺序</t>
+          <t>（待填）未见之道 8 点</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Entwined → Unseen Path → Heartwood…</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" outlineLevel="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>毕业</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>（待填）未见之道 8 点</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
           <t>暴击 / 伤害小点收尾</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>▸ 过渡计划（待补充 · 占位模板）</t>
         </is>
       </c>
     </row>
+    <row r="95" outlineLevel="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>记录等级里程碑、天赋重洗与装备更换节点，便于复刻开荒路线。</t>
+        </is>
+      </c>
+    </row>
     <row r="96" outlineLevel="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>记录等级里程碑、天赋重洗与装备更换节点，便于复刻开荒路线。</t>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>天赋变化</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>装备变化</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>里程碑</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>天赋变化</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>装备变化</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Lv.28 前</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>（待填）</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>基础图腾开荒</t>
         </is>
       </c>
     </row>
     <row r="98" outlineLevel="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Lv.28 前</t>
+          <t>Lv.45</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -5590,14 +6031,14 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>基础图腾开荒</t>
+          <t>诅咒 + 低血过渡</t>
         </is>
       </c>
     </row>
     <row r="99" outlineLevel="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Lv.45</t>
+          <t>Lv.65</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -5612,19 +6053,19 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>（待填）</t>
+          <t>Soul Mantle 入手</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>诅咒 + 低血过渡</t>
+          <t>自诅咒伤害链启动</t>
         </is>
       </c>
     </row>
     <row r="100" outlineLevel="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Lv.65</t>
+          <t>Lv.80+</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -5639,24 +6080,24 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Soul Mantle 入手</t>
+          <t>II 组装备就位</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>自诅咒伤害链启动</t>
+          <t>洗 24 点防御专精</t>
         </is>
       </c>
     </row>
     <row r="101" outlineLevel="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Lv.80+</t>
+          <t>毕业</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5666,110 +6107,86 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>II 组装备就位</t>
+          <t>全暗金 + 涂油</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>洗 24 点防御专精</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>毕业</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>（待填）</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>全暗金 + 涂油</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
           <t>对照 ninja 快照微调</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>▸ Warding Fetish 涂油（贴图）</t>
         </is>
       </c>
     </row>
-    <row r="104" outlineLevel="1">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="103" outlineLevel="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>部位</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>贴图</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>装备词条</t>
         </is>
       </c>
     </row>
-    <row r="105" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A105" s="10" t="inlineStr">
+    <row r="104" outlineLevel="1" ht="28" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>涂油</t>
         </is>
       </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>Warding Fetish</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="n"/>
-    </row>
-    <row r="106" outlineLevel="1" ht="84" customHeight="1">
-      <c r="A106" s="12" t="n"/>
-      <c r="B106" s="13" t="inlineStr"/>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Warding Fetish
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>守護神器
+(Warding Fetish)</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="n"/>
+    </row>
+    <row r="105" outlineLevel="1" ht="132" customHeight="1">
+      <c r="A105" s="12" t="n"/>
+      <c r="B105" s="13" t="inlineStr"/>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>守護神器 (Warding Fetish)
+■ 你身上每有一個詛咒，增加30%傷害
+■ 減少30%你身上的詛咒效果
+■ 增加60%來自已裝備法器的能量護盾
 ▶ BD 用途：涂油核心：每诅咒 +30% 伤害，-30% 诅咒效果
 🔗 https://poe2db.tw/tw/Warding_Fetish
 ▶ 自诅咒 → 伤害转化核心</t>
         </is>
       </c>
     </row>
-    <row r="107" outlineLevel="1"/>
+    <row r="106" outlineLevel="1"/>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A105:A106"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A96:F96"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A43:F43"/>
   </mergeCells>
@@ -5832,7 +6249,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Grim Pillars 436,868</t>
+          <t>Grim Pillars 255,178</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00-目录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01-机制" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02-武器组" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03-天赋" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04-常见问题" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-目录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-机制" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-武器组" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-天赋" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-常见问题" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -295,13 +295,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -320,13 +320,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -345,13 +345,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -370,13 +370,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -395,13 +395,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -420,13 +420,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -445,13 +445,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -470,13 +470,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -495,13 +495,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -520,13 +520,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -545,13 +545,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -570,13 +570,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -595,13 +595,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -620,13 +620,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -645,13 +645,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -670,13 +670,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -695,13 +695,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -720,13 +720,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -745,13 +745,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -770,13 +770,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -795,13 +795,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -820,13 +820,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -845,13 +845,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -870,13 +870,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -895,13 +895,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -920,13 +920,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -945,13 +945,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -970,13 +970,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -995,13 +995,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1020,13 +1020,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1045,13 +1045,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1070,13 +1070,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1095,13 +1095,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1120,13 +1120,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1145,13 +1145,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1170,13 +1170,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1195,13 +1195,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1220,13 +1220,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1245,13 +1245,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1270,13 +1270,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1295,13 +1295,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1320,13 +1320,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1345,13 +1345,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1370,13 +1370,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1385,7 +1385,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1400,13 +1400,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1425,13 +1425,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -3460,7 +3460,7 @@
 ★ +1召喚圖騰最大數量
 ★ 當你的圖騰死亡時，會對你施加一個隨機的詛咒，並無視詛咒數量上限
 ★ 減少(20—30)%圖騰生命
-「The greatest mistakes cause suffering
+「The greatest mistakes cause suffering
 long after they have been made」
 ▶ BD 用途：BD核心：自诅咒 +1 图腾。突变词缀 20% 图腾伤害/诅咒
 🔗 https://poe2db.tw/tw/Soul_Mantle
@@ -3558,9 +3558,9 @@
 ★ +(20—30)點敏捷
 ★ 增加25%光線範圍
 ★ 賦予引導暴風神殿的效果
-「"Deep in thought, you would tremble the very air before you.
-Wreathed in light, you nurtured them all. 
-And yet... Your nature became you."
+「"Deep in thought, you would tremble the very air before you.
+Wreathed in light, you nurtured them all. 
+And yet... Your nature became you."
 The Dreamer mused with aching heart, as remnants of forking tendrils burst forth.」
 ▶ BD 用途：副手权杖：Spirit 光环 + 闪电伤害
 🔗 https://poe2db.tw/tw/Guiding_Palm_of_the_Mind
@@ -3813,7 +3813,7 @@
 ★ 盟友對你標記的目標增加(50—100)%傷害
 ★ 你可以擁有任意數量的不同類型盟友
 ★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
+「Darkness howls through ancient bones, a wistful cry
 on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
@@ -3849,7 +3849,7 @@
 ★ +(20—30)%閃電抗性
 ★ 增加40%魔力回復率
 ★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
+「A flash of blue, a stormcloud's kiss,
 her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
@@ -3905,7 +3905,7 @@
 底材：Diamond
 需求:  等級 20
 ★ 配置Passive Skill
-「If you're going to act like you're better
+「If you're going to act like you're better
 than everyone else, make sure you are.」
 ▶ BD 用途：可选基石珠宝
 🔗 https://poe2db.tw/tw/Megalomaniac</t>
@@ -3937,7 +3937,7 @@
 需求:  等級 20
 ★ Custom Desecrated prefix
 ★ Custom Desecrated suffix
-「Countless souls scream in agonising harmony,
+「Countless souls scream in agonising harmony,
 forever sinking under the weight of the newly dead.」
 ▶ BD 用途：井心珠宝，强力天赋加成
 🔗 https://poe2db.tw/tw/Heart_of_the_Well</t>
@@ -4057,8 +4057,8 @@
 ★ 減少(50—60)%充能
 ★ 效果期間內來自藥劑的魔力回復可以溢出最大魔力
 ★ 效果期間內若你沒有符文保護，則每秒失去5%生命
-「Uhtred drank. Verisium burned through his veins.
-He gazed at death's face. With all his strength,
+「Uhtred drank. Verisium burned through his veins.
+He gazed at death's face. With all his strength,
 he turned instead to the stars, and witnessed Truth.」
 ▶ BD 用途：卡古尔主题魔力药剂
 🔗 https://poe2db.tw/tw/Uhtreds_Chalice</t>
@@ -4090,7 +4090,7 @@
 需求:  等級 50
 ■ 當你擊殺稀有或傳奇敵人時使用
 ★ Possessed by Spirit Of The Azmeri Spirit for (10–20) seconds on use
-「To become a warrior and a hunter, each young
+「To become a warrior and a hunter, each young
 Azmeri must prove themselves before the Spirit.」
 ▶ BD 用途：金色护符，生存/机动
 🔗 https://poe2db.tw/tw/Rite_of_Passage</t>
@@ -4123,7 +4123,7 @@
 ■ 當你被感電時使用
 ★ 增加(10—20)%持續時間
 ★ 在效果期間，敵人擊中你的閃電傷害相當不幸
-「The most beloved member of every Brinerot crew
+「The most beloved member of every Brinerot crew
 is the one that refuses to do any actual work.」
 ▶ BD 用途：接地护符，防闪电
 🔗 https://poe2db.tw/tw/The_Black_Cat</t>
@@ -4155,8 +4155,8 @@
 需求:  等級 10
 ■ 當你受到緩速效果影響時使用
 ★ 在效果期間賦予猛攻
-「"When the headsman's blade swings,
-your last moments stretch to eternity."
+「"When the headsman's blade swings,
+your last moments stretch to eternity."
 - Vorm, the Twice-Pardoned」
 ▶ BD 用途：银色护符
 🔗 https://poe2db.tw/tw/The_Fall_of_the_Axe</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00-目录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-机制" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-武器组" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-天赋" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-常见问题" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="00-目录" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01-机制" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02-武器组" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03-天赋" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04-常见问题" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -295,13 +295,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -320,13 +320,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -345,13 +345,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -370,13 +370,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -395,13 +395,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -420,13 +420,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -445,13 +445,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -470,13 +470,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -495,13 +495,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -520,13 +520,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -545,13 +545,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -570,13 +570,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -595,13 +595,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -620,13 +620,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -645,13 +645,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -670,13 +670,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -695,13 +695,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -720,13 +720,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -745,13 +745,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -770,13 +770,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -795,13 +795,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -820,13 +820,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -845,13 +845,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -870,13 +870,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -895,13 +895,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -920,13 +920,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -945,13 +945,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -970,13 +970,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -995,13 +995,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1020,13 +1020,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1045,13 +1045,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1070,13 +1070,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1095,13 +1095,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1120,13 +1120,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1145,13 +1145,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1170,13 +1170,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1195,13 +1195,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1220,13 +1220,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1245,13 +1245,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1270,13 +1270,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1295,13 +1295,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1320,13 +1320,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1345,13 +1345,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1370,13 +1370,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1385,7 +1385,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1400,13 +1400,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1425,13 +1425,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -3460,7 +3460,7 @@
 ★ +1召喚圖騰最大數量
 ★ 當你的圖騰死亡時，會對你施加一個隨機的詛咒，並無視詛咒數量上限
 ★ 減少(20—30)%圖騰生命
-「The greatest mistakes cause suffering
+「The greatest mistakes cause suffering
 long after they have been made」
 ▶ BD 用途：BD核心：自诅咒 +1 图腾。突变词缀 20% 图腾伤害/诅咒
 🔗 https://poe2db.tw/tw/Soul_Mantle
@@ -3558,9 +3558,9 @@
 ★ +(20—30)點敏捷
 ★ 增加25%光線範圍
 ★ 賦予引導暴風神殿的效果
-「"Deep in thought, you would tremble the very air before you.
-Wreathed in light, you nurtured them all. 
-And yet... Your nature became you."
+「"Deep in thought, you would tremble the very air before you.
+Wreathed in light, you nurtured them all. 
+And yet... Your nature became you."
 The Dreamer mused with aching heart, as remnants of forking tendrils burst forth.」
 ▶ BD 用途：副手权杖：Spirit 光环 + 闪电伤害
 🔗 https://poe2db.tw/tw/Guiding_Palm_of_the_Mind
@@ -3813,7 +3813,7 @@
 ★ 盟友對你標記的目標增加(50—100)%傷害
 ★ 你可以擁有任意數量的不同類型盟友
 ★ discipline art variation 1
-「Darkness howls through ancient bones, a wistful cry
+「Darkness howls through ancient bones, a wistful cry
 on hollow winds. The moon listens. The pack gathers.」
 ▶ BD 用途：II组主手：+58% Spirit、+6全属性，切换时保光环
 🔗 https://poe2db.tw/tw/Sylvans_Effigy
@@ -3849,7 +3849,7 @@
 ★ +(20—30)%閃電抗性
 ★ 增加40%魔力回復率
 ★ 站立時，增加40%魔力回復率
-「A flash of blue, a stormcloud's kiss,
+「A flash of blue, a stormcloud's kiss,
 her motionless dance the pulse of bliss」
 ▶ BD 用途：II组副手：+30%闪电抗、+5%闪电抗上限、70% ES
 🔗 https://poe2db.tw/tw/The_Eternal_Spark
@@ -3905,7 +3905,7 @@
 底材：Diamond
 需求:  等級 20
 ★ 配置Passive Skill
-「If you're going to act like you're better
+「If you're going to act like you're better
 than everyone else, make sure you are.」
 ▶ BD 用途：可选基石珠宝
 🔗 https://poe2db.tw/tw/Megalomaniac</t>
@@ -3937,7 +3937,7 @@
 需求:  等級 20
 ★ Custom Desecrated prefix
 ★ Custom Desecrated suffix
-「Countless souls scream in agonising harmony,
+「Countless souls scream in agonising harmony,
 forever sinking under the weight of the newly dead.」
 ▶ BD 用途：井心珠宝，强力天赋加成
 🔗 https://poe2db.tw/tw/Heart_of_the_Well</t>
@@ -4057,8 +4057,8 @@
 ★ 減少(50—60)%充能
 ★ 效果期間內來自藥劑的魔力回復可以溢出最大魔力
 ★ 效果期間內若你沒有符文保護，則每秒失去5%生命
-「Uhtred drank. Verisium burned through his veins.
-He gazed at death's face. With all his strength,
+「Uhtred drank. Verisium burned through his veins.
+He gazed at death's face. With all his strength,
 he turned instead to the stars, and witnessed Truth.」
 ▶ BD 用途：卡古尔主题魔力药剂
 🔗 https://poe2db.tw/tw/Uhtreds_Chalice</t>
@@ -4090,7 +4090,7 @@
 需求:  等級 50
 ■ 當你擊殺稀有或傳奇敵人時使用
 ★ Possessed by Spirit Of The Azmeri Spirit for (10–20) seconds on use
-「To become a warrior and a hunter, each young
+「To become a warrior and a hunter, each young
 Azmeri must prove themselves before the Spirit.」
 ▶ BD 用途：金色护符，生存/机动
 🔗 https://poe2db.tw/tw/Rite_of_Passage</t>
@@ -4123,7 +4123,7 @@
 ■ 當你被感電時使用
 ★ 增加(10—20)%持續時間
 ★ 在效果期間，敵人擊中你的閃電傷害相當不幸
-「The most beloved member of every Brinerot crew
+「The most beloved member of every Brinerot crew
 is the one that refuses to do any actual work.」
 ▶ BD 用途：接地护符，防闪电
 🔗 https://poe2db.tw/tw/The_Black_Cat</t>
@@ -4155,8 +4155,8 @@
 需求:  等級 10
 ■ 當你受到緩速效果影響時使用
 ★ 在效果期間賦予猛攻
-「"When the headsman's blade swings,
-your last moments stretch to eternity."
+「"When the headsman's blade swings,
+your last moments stretch to eternity."
 - Vorm, the Twice-Pardoned」
 ▶ BD 用途：银色护符
 🔗 https://poe2db.tw/tw/The_Fall_of_the_Axe</t>

--- a/Grim_Pillars_Oracle_BD指南.xlsx
+++ b/Grim_Pillars_Oracle_BD指南.xlsx
@@ -3072,7 +3072,7 @@
       <c r="D26" s="11" t="inlineStr">
         <is>
           <t>神使之心
-(Seraph's Heart)</t>
+(Date)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
